--- a/Заявки поставщикам (авторасчёт).xlsx
+++ b/Заявки поставщикам (авторасчёт).xlsx
@@ -23980,9 +23980,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
-    <col min="5" max="8" width="16" customWidth="1"/>
+    <col min="2" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="7" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -24003,25 +24004,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Группа номенклатуры</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Артикул</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Номенклатура</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Остаток</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Продажи 12м</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Запас (дней)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Заморожено (руб.)</t>
         </is>
@@ -24043,19 +24054,29 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 краски растворители</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Аммиачная селитра 1кг</t>
         </is>
       </c>
-      <c r="E2" s="6">
+      <c r="G2" s="6">
         <v>22</v>
       </c>
-      <c r="F2" s="6">
+      <c r="H2" s="6">
         <v>14</v>
       </c>
-      <c r="G2" s="4">
+      <c r="I2" s="4">
         <v>954.1</v>
       </c>
-      <c r="H2" s="4">
+      <c r="J2" s="4">
         <v>13.36</v>
       </c>
     </row>
@@ -24075,19 +24096,29 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 краски растворители</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Грунтовка ВД-АК-08 FLAGMAN1л</t>
         </is>
       </c>
-      <c r="E3" s="6">
+      <c r="G3" s="6">
         <v>6</v>
       </c>
-      <c r="F3" s="6">
+      <c r="H3" s="6">
         <v>1</v>
       </c>
-      <c r="G3" s="4">
+      <c r="I3" s="4">
         <v>879.1</v>
       </c>
-      <c r="H3" s="4">
+      <c r="J3" s="4">
         <v>13.34</v>
       </c>
     </row>
@@ -24107,19 +24138,29 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 краски растворители</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Грунтовка ГФ-021 кр-кор. 1кг</t>
         </is>
       </c>
-      <c r="E4" s="6">
+      <c r="G4" s="6">
         <v>11</v>
       </c>
-      <c r="F4" s="6">
+      <c r="H4" s="6">
         <v>3</v>
       </c>
-      <c r="G4" s="4">
+      <c r="I4" s="4">
         <v>817.3</v>
       </c>
-      <c r="H4" s="4">
+      <c r="J4" s="4">
         <v>27.53</v>
       </c>
     </row>
@@ -24139,19 +24180,29 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 краски растворители</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SM-26804-1</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Эмаль 520мл. аэроз.термост.черн.STARFIX</t>
         </is>
       </c>
-      <c r="E5" s="6">
+      <c r="G5" s="6">
         <v>6</v>
       </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
         <v>785.5</v>
       </c>
-      <c r="H5" s="4">
+      <c r="J5" s="4">
         <v>22.96</v>
       </c>
     </row>
@@ -24171,19 +24222,29 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 краски растворители</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Эмаль ПФ-115 салатовая 2л (1,8кг)</t>
         </is>
       </c>
-      <c r="E6" s="6">
+      <c r="G6" s="6">
         <v>5</v>
       </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
         <v>999</v>
       </c>
-      <c r="H6" s="4">
+      <c r="J6" s="4">
         <v>40.98</v>
       </c>
     </row>
@@ -24203,19 +24264,29 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 краски растворители</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Эмаль термост. 0,4кг. серебристая Elcon</t>
         </is>
       </c>
-      <c r="E7" s="6">
+      <c r="G7" s="6">
         <v>4</v>
       </c>
-      <c r="F7" s="6">
+      <c r="H7" s="6">
         <v>2</v>
       </c>
-      <c r="G7" s="4">
+      <c r="I7" s="4">
         <v>999</v>
       </c>
-      <c r="H7" s="4">
+      <c r="J7" s="4">
         <v>35.14</v>
       </c>
     </row>
@@ -24235,19 +24306,29 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Бирка для ключей</t>
         </is>
       </c>
-      <c r="E8" s="6">
+      <c r="G8" s="6">
         <v>60</v>
       </c>
-      <c r="F8" s="6">
+      <c r="H8" s="6">
         <v>15</v>
       </c>
-      <c r="G8" s="4">
+      <c r="I8" s="4">
         <v>713</v>
       </c>
-      <c r="H8" s="4">
+      <c r="J8" s="4">
         <v>25.36</v>
       </c>
     </row>
@@ -24267,19 +24348,29 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Задвижка Аллюр</t>
         </is>
       </c>
-      <c r="E9" s="6">
+      <c r="G9" s="6">
         <v>12</v>
       </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
         <v>999</v>
       </c>
-      <c r="H9" s="4">
+      <c r="J9" s="4">
         <v>32.3</v>
       </c>
     </row>
@@ -24299,19 +24390,29 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Задвижка дверная ЗН-40 SL</t>
         </is>
       </c>
-      <c r="E10" s="6">
+      <c r="G10" s="6">
         <v>9</v>
       </c>
-      <c r="F10" s="6">
+      <c r="H10" s="6">
         <v>5</v>
       </c>
-      <c r="G10" s="4">
+      <c r="I10" s="4">
         <v>999</v>
       </c>
-      <c r="H10" s="4">
+      <c r="J10" s="4">
         <v>27.54</v>
       </c>
     </row>
@@ -24331,19 +24432,29 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Задвижка накл. ЗТ6 полимер</t>
         </is>
       </c>
-      <c r="E11" s="6">
+      <c r="G11" s="6">
         <v>9</v>
       </c>
-      <c r="F11" s="6">
+      <c r="H11" s="6">
         <v>11</v>
       </c>
-      <c r="G11" s="4">
+      <c r="I11" s="4">
         <v>378.9</v>
       </c>
-      <c r="H11" s="4">
+      <c r="J11" s="4">
         <v>3.87</v>
       </c>
     </row>
@@ -24363,19 +24474,29 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Замок навесной ВС1Ч-360 9мм 5кл</t>
         </is>
       </c>
-      <c r="E12" s="6">
+      <c r="G12" s="6">
         <v>6</v>
       </c>
-      <c r="F12" s="6">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4">
+      <c r="H12" s="6">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4">
         <v>999</v>
       </c>
-      <c r="H12" s="4">
+      <c r="J12" s="4">
         <v>55.68</v>
       </c>
     </row>
@@ -24395,19 +24516,29 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Защелка врезная L45-8 SN мат.ник.АЛЛЮР</t>
         </is>
       </c>
-      <c r="E13" s="6">
+      <c r="G13" s="6">
         <v>14</v>
       </c>
-      <c r="F13" s="6">
+      <c r="H13" s="6">
         <v>10</v>
       </c>
-      <c r="G13" s="4">
+      <c r="I13" s="4">
         <v>515.6</v>
       </c>
-      <c r="H13" s="4">
+      <c r="J13" s="4">
         <v>24.67</v>
       </c>
     </row>
@@ -24427,19 +24558,29 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Комплект ручек Аллюр  АРТ Адель</t>
         </is>
       </c>
-      <c r="E14" s="6">
+      <c r="G14" s="6">
         <v>5</v>
       </c>
-      <c r="F14" s="6">
+      <c r="H14" s="6">
         <v>1</v>
       </c>
-      <c r="G14" s="4">
+      <c r="I14" s="4">
         <v>999</v>
       </c>
-      <c r="H14" s="4">
+      <c r="J14" s="4">
         <v>74.35</v>
       </c>
     </row>
@@ -24459,19 +24600,29 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Кронштейн 200*250 кор полимер</t>
         </is>
       </c>
-      <c r="E15" s="6">
+      <c r="G15" s="6">
         <v>10</v>
       </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
+      <c r="H15" s="6">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
         <v>999</v>
       </c>
-      <c r="H15" s="4">
+      <c r="J15" s="4">
         <v>13.28</v>
       </c>
     </row>
@@ -24491,19 +24642,29 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Кронштейн 250*300кор полимер</t>
         </is>
       </c>
-      <c r="E16" s="6">
+      <c r="G16" s="6">
         <v>10</v>
       </c>
-      <c r="F16" s="6">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4">
+      <c r="H16" s="6">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
         <v>999</v>
       </c>
-      <c r="H16" s="4">
+      <c r="J16" s="4">
         <v>22.64</v>
       </c>
     </row>
@@ -24523,19 +24684,29 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Крючок вешалка №24 зол</t>
         </is>
       </c>
-      <c r="E17" s="6">
+      <c r="G17" s="6">
         <v>10</v>
       </c>
-      <c r="F17" s="6">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4">
+      <c r="H17" s="6">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4">
         <v>999</v>
       </c>
-      <c r="H17" s="4">
+      <c r="J17" s="4">
         <v>13.04</v>
       </c>
     </row>
@@ -24555,19 +24726,29 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMP-74243-1</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Крючок вешалка №25 пол</t>
         </is>
       </c>
-      <c r="E18" s="6">
+      <c r="G18" s="6">
         <v>5</v>
       </c>
-      <c r="F18" s="6">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4">
+      <c r="H18" s="6">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4">
         <v>999</v>
       </c>
-      <c r="H18" s="4">
+      <c r="J18" s="4">
         <v>5.88</v>
       </c>
     </row>
@@ -24587,19 +24768,29 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMP-88801-1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Крючок вешалка №25 хром</t>
         </is>
       </c>
-      <c r="E19" s="6">
+      <c r="G19" s="6">
         <v>5</v>
       </c>
-      <c r="F19" s="6">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4">
+      <c r="H19" s="6">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
         <v>999</v>
       </c>
-      <c r="H19" s="4">
+      <c r="J19" s="4">
         <v>5.61</v>
       </c>
     </row>
@@ -24619,19 +24810,29 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMP-21831-1</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Крючок вешалка №25 черн</t>
         </is>
       </c>
-      <c r="E20" s="6">
+      <c r="G20" s="6">
         <v>5</v>
       </c>
-      <c r="F20" s="6">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4">
+      <c r="H20" s="6">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4">
         <v>999</v>
       </c>
-      <c r="H20" s="4">
+      <c r="J20" s="4">
         <v>5.7</v>
       </c>
     </row>
@@ -24651,19 +24852,29 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Крючок вешалка №4 полимер бр</t>
         </is>
       </c>
-      <c r="E21" s="6">
+      <c r="G21" s="6">
         <v>9</v>
       </c>
-      <c r="F21" s="6">
+      <c r="H21" s="6">
         <v>1</v>
       </c>
-      <c r="G21" s="4">
+      <c r="I21" s="4">
         <v>945.3</v>
       </c>
-      <c r="H21" s="4">
+      <c r="J21" s="4">
         <v>6.56</v>
       </c>
     </row>
@@ -24683,19 +24894,29 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Магнит меб.L-60 h-15</t>
         </is>
       </c>
-      <c r="E22" s="6">
+      <c r="G22" s="6">
         <v>42</v>
       </c>
-      <c r="F22" s="6">
+      <c r="H22" s="6">
         <v>38</v>
       </c>
-      <c r="G22" s="4">
+      <c r="I22" s="4">
         <v>650.9</v>
       </c>
-      <c r="H22" s="4">
+      <c r="J22" s="4">
         <v>12.81</v>
       </c>
     </row>
@@ -24715,19 +24936,29 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Набор крепления ручек к квадрату</t>
         </is>
       </c>
-      <c r="E23" s="6">
+      <c r="G23" s="6">
         <v>15</v>
       </c>
-      <c r="F23" s="6">
+      <c r="H23" s="6">
         <v>4</v>
       </c>
-      <c r="G23" s="4">
+      <c r="I23" s="4">
         <v>999</v>
       </c>
-      <c r="H23" s="4">
+      <c r="J23" s="4">
         <v>11.13</v>
       </c>
     </row>
@@ -24747,19 +24978,29 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Набор крючков из кор.ст.1001</t>
         </is>
       </c>
-      <c r="E24" s="6">
+      <c r="G24" s="6">
         <v>4</v>
       </c>
-      <c r="F24" s="6">
+      <c r="H24" s="6">
         <v>1</v>
       </c>
-      <c r="G24" s="4">
+      <c r="I24" s="4">
         <v>984</v>
       </c>
-      <c r="H24" s="4">
+      <c r="J24" s="4">
         <v>5</v>
       </c>
     </row>
@@ -24779,19 +25020,29 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Накладка дверная 50мм на цилиндр.</t>
         </is>
       </c>
-      <c r="E25" s="6">
+      <c r="G25" s="6">
         <v>11</v>
       </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
+      <c r="H25" s="6">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4">
         <v>999</v>
       </c>
-      <c r="H25" s="4">
+      <c r="J25" s="4">
         <v>20.98</v>
       </c>
     </row>
@@ -24811,19 +25062,29 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Накладка для ц/м АЛЛЮР</t>
         </is>
       </c>
-      <c r="E26" s="6">
+      <c r="G26" s="6">
         <v>7</v>
       </c>
-      <c r="F26" s="6">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
+      <c r="H26" s="6">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4">
         <v>999</v>
       </c>
-      <c r="H26" s="4">
+      <c r="J26" s="4">
         <v>33.4</v>
       </c>
     </row>
@@ -24843,19 +25104,29 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Направляющие шариковые 35-500</t>
         </is>
       </c>
-      <c r="E27" s="6">
+      <c r="G27" s="6">
         <v>5</v>
       </c>
-      <c r="F27" s="6">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4">
+      <c r="H27" s="6">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4">
         <v>999</v>
       </c>
-      <c r="H27" s="4">
+      <c r="J27" s="4">
         <v>26.79</v>
       </c>
     </row>
@@ -24875,19 +25146,29 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Номерок дверной из пл.</t>
         </is>
       </c>
-      <c r="E28" s="6">
+      <c r="G28" s="6">
         <v>14</v>
       </c>
-      <c r="F28" s="6">
+      <c r="H28" s="6">
         <v>7</v>
       </c>
-      <c r="G28" s="4">
+      <c r="I28" s="4">
         <v>999</v>
       </c>
-      <c r="H28" s="4">
+      <c r="J28" s="4">
         <v>6.69</v>
       </c>
     </row>
@@ -24907,19 +25188,29 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ограничитель открыв. окна</t>
         </is>
       </c>
-      <c r="E29" s="6">
+      <c r="G29" s="6">
         <v>10</v>
       </c>
-      <c r="F29" s="6">
-        <v>0</v>
-      </c>
-      <c r="G29" s="4">
+      <c r="H29" s="6">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4">
         <v>999</v>
       </c>
-      <c r="H29" s="4">
+      <c r="J29" s="4">
         <v>9.2</v>
       </c>
     </row>
@@ -24939,19 +25230,29 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ограничитель открыв. окна L105</t>
         </is>
       </c>
-      <c r="E30" s="6">
+      <c r="G30" s="6">
         <v>10</v>
       </c>
-      <c r="F30" s="6">
-        <v>0</v>
-      </c>
-      <c r="G30" s="4">
+      <c r="H30" s="6">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4">
         <v>999</v>
       </c>
-      <c r="H30" s="4">
+      <c r="J30" s="4">
         <v>11.36</v>
       </c>
     </row>
@@ -24971,19 +25272,29 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ограничитель открыв. окна L165</t>
         </is>
       </c>
-      <c r="E31" s="6">
+      <c r="G31" s="6">
         <v>8</v>
       </c>
-      <c r="F31" s="6">
+      <c r="H31" s="6">
         <v>2</v>
       </c>
-      <c r="G31" s="4">
+      <c r="I31" s="4">
         <v>877.6</v>
       </c>
-      <c r="H31" s="4">
+      <c r="J31" s="4">
         <v>5.79</v>
       </c>
     </row>
@@ -25003,19 +25314,29 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Опора колесная 50 со штырем</t>
         </is>
       </c>
-      <c r="E32" s="6">
+      <c r="G32" s="6">
         <v>6</v>
       </c>
-      <c r="F32" s="6">
+      <c r="H32" s="6">
         <v>1</v>
       </c>
-      <c r="G32" s="4">
+      <c r="I32" s="4">
         <v>999</v>
       </c>
-      <c r="H32" s="4">
+      <c r="J32" s="4">
         <v>2.54</v>
       </c>
     </row>
@@ -25035,19 +25356,29 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMF-5968</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Опора мебельная круг. 79-86мм</t>
         </is>
       </c>
-      <c r="E33" s="6">
+      <c r="G33" s="6">
         <v>8</v>
       </c>
-      <c r="F33" s="6">
-        <v>0</v>
-      </c>
-      <c r="G33" s="4">
+      <c r="H33" s="6">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4">
         <v>999</v>
       </c>
-      <c r="H33" s="4">
+      <c r="J33" s="4">
         <v>21.72</v>
       </c>
     </row>
@@ -25067,19 +25398,29 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Петля гаражная 10*60 каплевидная</t>
         </is>
       </c>
-      <c r="E34" s="6">
+      <c r="G34" s="6">
         <v>23</v>
       </c>
-      <c r="F34" s="6">
+      <c r="H34" s="6">
         <v>1</v>
       </c>
-      <c r="G34" s="4">
+      <c r="I34" s="4">
         <v>999</v>
       </c>
-      <c r="H34" s="4">
+      <c r="J34" s="4">
         <v>40.32</v>
       </c>
     </row>
@@ -25099,19 +25440,29 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Петля гаражная с шар под сварку 18*120</t>
         </is>
       </c>
-      <c r="E35" s="6">
+      <c r="G35" s="6">
         <v>10</v>
       </c>
-      <c r="F35" s="6">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4">
+      <c r="H35" s="6">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4">
         <v>999</v>
       </c>
-      <c r="H35" s="4">
+      <c r="J35" s="4">
         <v>25.92</v>
       </c>
     </row>
@@ -25131,19 +25482,29 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Петля дверная 2043 100*70 2шт.</t>
         </is>
       </c>
-      <c r="E36" s="6">
+      <c r="G36" s="6">
         <v>4</v>
       </c>
-      <c r="F36" s="6">
+      <c r="H36" s="6">
         <v>2</v>
       </c>
-      <c r="G36" s="4">
+      <c r="I36" s="4">
         <v>924.9</v>
       </c>
-      <c r="H36" s="4">
+      <c r="J36" s="4">
         <v>12.02</v>
       </c>
     </row>
@@ -25163,19 +25524,29 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Петля карточная  140*34 цинк</t>
         </is>
       </c>
-      <c r="E37" s="6">
+      <c r="G37" s="6">
         <v>20</v>
       </c>
-      <c r="F37" s="6">
+      <c r="H37" s="6">
         <v>6</v>
       </c>
-      <c r="G37" s="4">
+      <c r="I37" s="4">
         <v>999</v>
       </c>
-      <c r="H37" s="4">
+      <c r="J37" s="4">
         <v>7.99</v>
       </c>
     </row>
@@ -25195,19 +25566,29 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Петля мебельная без вр.104*44 Stahlburo</t>
         </is>
       </c>
-      <c r="E38" s="6">
+      <c r="G38" s="6">
         <v>4</v>
       </c>
-      <c r="F38" s="6">
-        <v>0</v>
-      </c>
-      <c r="G38" s="4">
+      <c r="H38" s="6">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4">
         <v>999</v>
       </c>
-      <c r="H38" s="4">
+      <c r="J38" s="4">
         <v>5.96</v>
       </c>
     </row>
@@ -25227,19 +25608,29 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Петля мебельная без вр.78*33 Stahlburo</t>
         </is>
       </c>
-      <c r="E39" s="6">
+      <c r="G39" s="6">
         <v>9</v>
       </c>
-      <c r="F39" s="6">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4">
+      <c r="H39" s="6">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4">
         <v>999</v>
       </c>
-      <c r="H39" s="4">
+      <c r="J39" s="4">
         <v>17.78</v>
       </c>
     </row>
@@ -25259,19 +25650,29 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Петля мебельная внутр. с доводчиком. 1111</t>
         </is>
       </c>
-      <c r="E40" s="6">
+      <c r="G40" s="6">
         <v>9</v>
       </c>
-      <c r="F40" s="6">
+      <c r="H40" s="6">
         <v>7</v>
       </c>
-      <c r="G40" s="4">
+      <c r="I40" s="4">
         <v>999</v>
       </c>
-      <c r="H40" s="4">
+      <c r="J40" s="4">
         <v>9.79</v>
       </c>
     </row>
@@ -25291,19 +25692,29 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Петля мебельная накладная А 362 А Soller</t>
         </is>
       </c>
-      <c r="E41" s="6">
+      <c r="G41" s="6">
         <v>8</v>
       </c>
-      <c r="F41" s="6">
-        <v>0</v>
-      </c>
-      <c r="G41" s="4">
+      <c r="H41" s="6">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4">
         <v>609.3</v>
       </c>
-      <c r="H41" s="4">
+      <c r="J41" s="4">
         <v>2.24</v>
       </c>
     </row>
@@ -25323,19 +25734,29 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Петля мебельная полунакладная  с довод. Stahlburo</t>
         </is>
       </c>
-      <c r="E42" s="6">
+      <c r="G42" s="6">
         <v>9</v>
       </c>
-      <c r="F42" s="6">
+      <c r="H42" s="6">
         <v>1</v>
       </c>
-      <c r="G42" s="4">
+      <c r="I42" s="4">
         <v>999</v>
       </c>
-      <c r="H42" s="4">
+      <c r="J42" s="4">
         <v>26.46</v>
       </c>
     </row>
@@ -25355,19 +25776,29 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Петля накладная ПНУ-100 пол/цинк</t>
         </is>
       </c>
-      <c r="E43" s="6">
+      <c r="G43" s="6">
         <v>18</v>
       </c>
-      <c r="F43" s="6">
+      <c r="H43" s="6">
         <v>2</v>
       </c>
-      <c r="G43" s="4">
+      <c r="I43" s="4">
         <v>999</v>
       </c>
-      <c r="H43" s="4">
+      <c r="J43" s="4">
         <v>33.93</v>
       </c>
     </row>
@@ -25387,19 +25818,29 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Петля-стрела ПС-160 пол.черн</t>
         </is>
       </c>
-      <c r="E44" s="6">
+      <c r="G44" s="6">
         <v>6</v>
       </c>
-      <c r="F44" s="6">
-        <v>0</v>
-      </c>
-      <c r="G44" s="4">
+      <c r="H44" s="6">
+        <v>0</v>
+      </c>
+      <c r="I44" s="4">
         <v>999</v>
       </c>
-      <c r="H44" s="4">
+      <c r="J44" s="4">
         <v>10.48</v>
       </c>
     </row>
@@ -25419,19 +25860,29 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CV-28968-1</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Пластина креп. 100*35</t>
         </is>
       </c>
-      <c r="E45" s="6">
+      <c r="G45" s="6">
         <v>7</v>
       </c>
-      <c r="F45" s="6">
-        <v>0</v>
-      </c>
-      <c r="G45" s="4">
+      <c r="H45" s="6">
+        <v>0</v>
+      </c>
+      <c r="I45" s="4">
         <v>999</v>
       </c>
-      <c r="H45" s="4">
+      <c r="J45" s="4">
         <v>1.06</v>
       </c>
     </row>
@@ -25451,19 +25902,29 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Пластина креп. 50*160*2,0</t>
         </is>
       </c>
-      <c r="E46" s="6">
+      <c r="G46" s="6">
         <v>51</v>
       </c>
-      <c r="F46" s="6">
+      <c r="H46" s="6">
         <v>31</v>
       </c>
-      <c r="G46" s="4">
+      <c r="I46" s="4">
         <v>999</v>
       </c>
-      <c r="H46" s="4">
+      <c r="J46" s="4">
         <v>26.07</v>
       </c>
     </row>
@@ -25483,19 +25944,29 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Пластина креп. 80*100*2,0</t>
         </is>
       </c>
-      <c r="E47" s="6">
+      <c r="G47" s="6">
         <v>14</v>
       </c>
-      <c r="F47" s="6">
+      <c r="H47" s="6">
         <v>2</v>
       </c>
-      <c r="G47" s="4">
+      <c r="I47" s="4">
         <v>968.5</v>
       </c>
-      <c r="H47" s="4">
+      <c r="J47" s="4">
         <v>4.41</v>
       </c>
     </row>
@@ -25515,19 +25986,29 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Пластина креп. 80*120*2,0</t>
         </is>
       </c>
-      <c r="E48" s="6">
+      <c r="G48" s="6">
         <v>19</v>
       </c>
-      <c r="F48" s="6">
+      <c r="H48" s="6">
         <v>11</v>
       </c>
-      <c r="G48" s="4">
+      <c r="I48" s="4">
         <v>542.5</v>
       </c>
-      <c r="H48" s="4">
+      <c r="J48" s="4">
         <v>2.69</v>
       </c>
     </row>
@@ -25547,19 +26028,29 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Пластина креп.ПК-100 цинк</t>
         </is>
       </c>
-      <c r="E49" s="6">
+      <c r="G49" s="6">
         <v>34</v>
       </c>
-      <c r="F49" s="6">
+      <c r="H49" s="6">
         <v>29</v>
       </c>
-      <c r="G49" s="4">
+      <c r="I49" s="4">
         <v>999</v>
       </c>
-      <c r="H49" s="4">
+      <c r="J49" s="4">
         <v>1.4</v>
       </c>
     </row>
@@ -25579,19 +26070,29 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMF-3101</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Подъёмник газовый 100N STARFIX</t>
         </is>
       </c>
-      <c r="E50" s="6">
+      <c r="G50" s="6">
         <v>4</v>
       </c>
-      <c r="F50" s="6">
-        <v>0</v>
-      </c>
-      <c r="G50" s="4">
+      <c r="H50" s="6">
+        <v>0</v>
+      </c>
+      <c r="I50" s="4">
         <v>999</v>
       </c>
-      <c r="H50" s="4">
+      <c r="J50" s="4">
         <v>5.64</v>
       </c>
     </row>
@@ -25611,19 +26112,29 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMF-6801</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Подъёмник газовый 120N STARFIX</t>
         </is>
       </c>
-      <c r="E51" s="6">
+      <c r="G51" s="6">
         <v>4</v>
       </c>
-      <c r="F51" s="6">
-        <v>0</v>
-      </c>
-      <c r="G51" s="4">
+      <c r="H51" s="6">
+        <v>0</v>
+      </c>
+      <c r="I51" s="4">
         <v>999</v>
       </c>
-      <c r="H51" s="4">
+      <c r="J51" s="4">
         <v>6.1</v>
       </c>
     </row>
@@ -25643,19 +26154,29 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ролик выкатной Н-34 цинк</t>
         </is>
       </c>
-      <c r="E52" s="6">
+      <c r="G52" s="6">
         <v>21</v>
       </c>
-      <c r="F52" s="6">
-        <v>0</v>
-      </c>
-      <c r="G52" s="4">
+      <c r="H52" s="6">
+        <v>0</v>
+      </c>
+      <c r="I52" s="4">
         <v>999</v>
       </c>
-      <c r="H52" s="4">
+      <c r="J52" s="4">
         <v>15.01</v>
       </c>
     </row>
@@ -25675,19 +26196,29 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ролик опорный малый 493-1 цинк</t>
         </is>
       </c>
-      <c r="E53" s="6">
+      <c r="G53" s="6">
         <v>12</v>
       </c>
-      <c r="F53" s="6">
-        <v>0</v>
-      </c>
-      <c r="G53" s="4">
+      <c r="H53" s="6">
+        <v>0</v>
+      </c>
+      <c r="I53" s="4">
         <v>649.3</v>
       </c>
-      <c r="H53" s="4">
+      <c r="J53" s="4">
         <v>4.63</v>
       </c>
     </row>
@@ -25707,19 +26238,29 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ролик опорный малый 493-2 цинк</t>
         </is>
       </c>
-      <c r="E54" s="6">
+      <c r="G54" s="6">
         <v>20</v>
       </c>
-      <c r="F54" s="6">
-        <v>0</v>
-      </c>
-      <c r="G54" s="4">
+      <c r="H54" s="6">
+        <v>0</v>
+      </c>
+      <c r="I54" s="4">
         <v>999</v>
       </c>
-      <c r="H54" s="4">
+      <c r="J54" s="4">
         <v>11.38</v>
       </c>
     </row>
@@ -25739,19 +26280,29 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка балкон. метал.№2С</t>
         </is>
       </c>
-      <c r="E55" s="6">
+      <c r="G55" s="6">
         <v>4</v>
       </c>
-      <c r="F55" s="6">
-        <v>0</v>
-      </c>
-      <c r="G55" s="4">
+      <c r="H55" s="6">
+        <v>0</v>
+      </c>
+      <c r="I55" s="4">
         <v>999</v>
       </c>
-      <c r="H55" s="4">
+      <c r="J55" s="4">
         <v>1.68</v>
       </c>
     </row>
@@ -25771,19 +26322,29 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка балкон. полимер мет</t>
         </is>
       </c>
-      <c r="E56" s="6">
+      <c r="G56" s="6">
         <v>5</v>
       </c>
-      <c r="F56" s="6">
-        <v>0</v>
-      </c>
-      <c r="G56" s="4">
+      <c r="H56" s="6">
+        <v>0</v>
+      </c>
+      <c r="I56" s="4">
         <v>999</v>
       </c>
-      <c r="H56" s="4">
+      <c r="J56" s="4">
         <v>2.46</v>
       </c>
     </row>
@@ -25803,19 +26364,29 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка для пластиковых окон  35мм.</t>
         </is>
       </c>
-      <c r="E57" s="6">
+      <c r="G57" s="6">
         <v>12</v>
       </c>
-      <c r="F57" s="6">
-        <v>0</v>
-      </c>
-      <c r="G57" s="4">
+      <c r="H57" s="6">
+        <v>0</v>
+      </c>
+      <c r="I57" s="4">
         <v>767.6</v>
       </c>
-      <c r="H57" s="4">
+      <c r="J57" s="4">
         <v>24.04</v>
       </c>
     </row>
@@ -25835,19 +26406,29 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка кнопка меб. А507</t>
         </is>
       </c>
-      <c r="E58" s="6">
+      <c r="G58" s="6">
         <v>19</v>
       </c>
-      <c r="F58" s="6">
+      <c r="H58" s="6">
         <v>1</v>
       </c>
-      <c r="G58" s="4">
+      <c r="I58" s="4">
         <v>999</v>
       </c>
-      <c r="H58" s="4">
+      <c r="J58" s="4">
         <v>25.05</v>
       </c>
     </row>
@@ -25867,19 +26448,29 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка кнопка меб. грибок</t>
         </is>
       </c>
-      <c r="E59" s="6">
+      <c r="G59" s="6">
         <v>16</v>
       </c>
-      <c r="F59" s="6">
+      <c r="H59" s="6">
         <v>6</v>
       </c>
-      <c r="G59" s="4">
+      <c r="I59" s="4">
         <v>999</v>
       </c>
-      <c r="H59" s="4">
+      <c r="J59" s="4">
         <v>31.8</v>
       </c>
     </row>
@@ -25899,19 +26490,29 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка кнопка меб.большая</t>
         </is>
       </c>
-      <c r="E60" s="6">
+      <c r="G60" s="6">
         <v>33</v>
       </c>
-      <c r="F60" s="6">
+      <c r="H60" s="6">
         <v>8</v>
       </c>
-      <c r="G60" s="4">
+      <c r="I60" s="4">
         <v>999</v>
       </c>
-      <c r="H60" s="4">
+      <c r="J60" s="4">
         <v>28.07</v>
       </c>
     </row>
@@ -25931,19 +26532,29 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка москитной сетки</t>
         </is>
       </c>
-      <c r="E61" s="6">
+      <c r="G61" s="6">
         <v>10</v>
       </c>
-      <c r="F61" s="6">
-        <v>0</v>
-      </c>
-      <c r="G61" s="4">
+      <c r="H61" s="6">
+        <v>0</v>
+      </c>
+      <c r="I61" s="4">
         <v>999</v>
       </c>
-      <c r="H61" s="4">
+      <c r="J61" s="4">
         <v>0.8</v>
       </c>
     </row>
@@ -25963,19 +26574,29 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка откидная цинк 100*80</t>
         </is>
       </c>
-      <c r="E62" s="6">
+      <c r="G62" s="6">
         <v>9</v>
       </c>
-      <c r="F62" s="6">
+      <c r="H62" s="6">
         <v>3</v>
       </c>
-      <c r="G62" s="4">
+      <c r="I62" s="4">
         <v>999</v>
       </c>
-      <c r="H62" s="4">
+      <c r="J62" s="4">
         <v>16.02</v>
       </c>
     </row>
@@ -25995,19 +26616,29 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка откидная цинк 85*70</t>
         </is>
       </c>
-      <c r="E63" s="6">
+      <c r="G63" s="6">
         <v>15</v>
       </c>
-      <c r="F63" s="6">
+      <c r="H63" s="6">
         <v>3</v>
       </c>
-      <c r="G63" s="4">
+      <c r="I63" s="4">
         <v>999</v>
       </c>
-      <c r="H63" s="4">
+      <c r="J63" s="4">
         <v>16.41</v>
       </c>
     </row>
@@ -26027,19 +26658,29 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка Р-1 пол</t>
         </is>
       </c>
-      <c r="E64" s="6">
+      <c r="G64" s="6">
         <v>16</v>
       </c>
-      <c r="F64" s="6">
+      <c r="H64" s="6">
         <v>4</v>
       </c>
-      <c r="G64" s="4">
+      <c r="I64" s="4">
         <v>999</v>
       </c>
-      <c r="H64" s="4">
+      <c r="J64" s="4">
         <v>18.98</v>
       </c>
     </row>
@@ -26059,19 +26700,29 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка Р-1 цинк</t>
         </is>
       </c>
-      <c r="E65" s="6">
+      <c r="G65" s="6">
         <v>12</v>
       </c>
-      <c r="F65" s="6">
+      <c r="H65" s="6">
         <v>8</v>
       </c>
-      <c r="G65" s="4">
+      <c r="I65" s="4">
         <v>708.3</v>
       </c>
-      <c r="H65" s="4">
+      <c r="J65" s="4">
         <v>5.27</v>
       </c>
     </row>
@@ -26091,19 +26742,29 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка скоба меб. 204-96</t>
         </is>
       </c>
-      <c r="E66" s="6">
+      <c r="G66" s="6">
         <v>21</v>
       </c>
-      <c r="F66" s="6">
+      <c r="H66" s="6">
         <v>7</v>
       </c>
-      <c r="G66" s="4">
+      <c r="I66" s="4">
         <v>999</v>
       </c>
-      <c r="H66" s="4">
+      <c r="J66" s="4">
         <v>21.43</v>
       </c>
     </row>
@@ -26123,19 +26784,29 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка скоба меб. 345-96</t>
         </is>
       </c>
-      <c r="E67" s="6">
+      <c r="G67" s="6">
         <v>20</v>
       </c>
-      <c r="F67" s="6">
+      <c r="H67" s="6">
         <v>2</v>
       </c>
-      <c r="G67" s="4">
+      <c r="I67" s="4">
         <v>999</v>
       </c>
-      <c r="H67" s="4">
+      <c r="J67" s="4">
         <v>30.74</v>
       </c>
     </row>
@@ -26155,19 +26826,29 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка скоба меб. 8926-128</t>
         </is>
       </c>
-      <c r="E68" s="6">
+      <c r="G68" s="6">
         <v>10</v>
       </c>
-      <c r="F68" s="6">
-        <v>0</v>
-      </c>
-      <c r="G68" s="4">
+      <c r="H68" s="6">
+        <v>0</v>
+      </c>
+      <c r="I68" s="4">
         <v>999</v>
       </c>
-      <c r="H68" s="4">
+      <c r="J68" s="4">
         <v>25.28</v>
       </c>
     </row>
@@ -26187,19 +26868,29 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка скоба меб. А300-128</t>
         </is>
       </c>
-      <c r="E69" s="6">
+      <c r="G69" s="6">
         <v>5</v>
       </c>
-      <c r="F69" s="6">
-        <v>0</v>
-      </c>
-      <c r="G69" s="4">
+      <c r="H69" s="6">
+        <v>0</v>
+      </c>
+      <c r="I69" s="4">
         <v>999</v>
       </c>
-      <c r="H69" s="4">
+      <c r="J69" s="4">
         <v>24.12</v>
       </c>
     </row>
@@ -26219,19 +26910,29 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка скоба меб. А300-96</t>
         </is>
       </c>
-      <c r="E70" s="6">
+      <c r="G70" s="6">
         <v>4</v>
       </c>
-      <c r="F70" s="6">
+      <c r="H70" s="6">
         <v>1</v>
       </c>
-      <c r="G70" s="4">
+      <c r="I70" s="4">
         <v>999</v>
       </c>
-      <c r="H70" s="4">
+      <c r="J70" s="4">
         <v>13.22</v>
       </c>
     </row>
@@ -26251,19 +26952,29 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка скоба меб. пол.серебро</t>
         </is>
       </c>
-      <c r="E71" s="6">
+      <c r="G71" s="6">
         <v>10</v>
       </c>
-      <c r="F71" s="6">
-        <v>0</v>
-      </c>
-      <c r="G71" s="4">
+      <c r="H71" s="6">
+        <v>0</v>
+      </c>
+      <c r="I71" s="4">
         <v>999</v>
       </c>
-      <c r="H71" s="4">
+      <c r="J71" s="4">
         <v>8.36</v>
       </c>
     </row>
@@ -26283,19 +26994,29 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка скоба меб. Р100-96</t>
         </is>
       </c>
-      <c r="E72" s="6">
+      <c r="G72" s="6">
         <v>20</v>
       </c>
-      <c r="F72" s="6">
-        <v>0</v>
-      </c>
-      <c r="G72" s="4">
+      <c r="H72" s="6">
+        <v>0</v>
+      </c>
+      <c r="I72" s="4">
         <v>999</v>
       </c>
-      <c r="H72" s="4">
+      <c r="J72" s="4">
         <v>37.08</v>
       </c>
     </row>
@@ -26315,19 +27036,29 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка-кнопка АР2704</t>
         </is>
       </c>
-      <c r="E73" s="6">
+      <c r="G73" s="6">
         <v>7</v>
       </c>
-      <c r="F73" s="6">
+      <c r="H73" s="6">
         <v>2</v>
       </c>
-      <c r="G73" s="4">
+      <c r="I73" s="4">
         <v>999</v>
       </c>
-      <c r="H73" s="4">
+      <c r="J73" s="4">
         <v>32.05</v>
       </c>
     </row>
@@ -26347,19 +27078,29 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка-скоба РС-100 зол. мет.</t>
         </is>
       </c>
-      <c r="E74" s="6">
+      <c r="G74" s="6">
         <v>5</v>
       </c>
-      <c r="F74" s="6">
-        <v>0</v>
-      </c>
-      <c r="G74" s="4">
+      <c r="H74" s="6">
+        <v>0</v>
+      </c>
+      <c r="I74" s="4">
         <v>999</v>
       </c>
-      <c r="H74" s="4">
+      <c r="J74" s="4">
         <v>12.54</v>
       </c>
     </row>
@@ -26379,19 +27120,29 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ручка-скоба РС-140 банная</t>
         </is>
       </c>
-      <c r="E75" s="6">
+      <c r="G75" s="6">
         <v>5</v>
       </c>
-      <c r="F75" s="6">
-        <v>0</v>
-      </c>
-      <c r="G75" s="4">
+      <c r="H75" s="6">
+        <v>0</v>
+      </c>
+      <c r="I75" s="4">
         <v>999</v>
       </c>
-      <c r="H75" s="4">
+      <c r="J75" s="4">
         <v>24.12</v>
       </c>
     </row>
@@ -26411,19 +27162,29 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Стяжки для крепления разд. ручек</t>
         </is>
       </c>
-      <c r="E76" s="6">
+      <c r="G76" s="6">
         <v>6</v>
       </c>
-      <c r="F76" s="6">
+      <c r="H76" s="6">
         <v>4</v>
       </c>
-      <c r="G76" s="4">
+      <c r="I76" s="4">
         <v>408.8</v>
       </c>
-      <c r="H76" s="4">
+      <c r="J76" s="4">
         <v>2.32</v>
       </c>
     </row>
@@ -26443,19 +27204,29 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Уголок крепеж фигур. 90*90*80*2,1усил</t>
         </is>
       </c>
-      <c r="E77" s="6">
+      <c r="G77" s="6">
         <v>5</v>
       </c>
-      <c r="F77" s="6">
-        <v>0</v>
-      </c>
-      <c r="G77" s="4">
+      <c r="H77" s="6">
+        <v>0</v>
+      </c>
+      <c r="I77" s="4">
         <v>999</v>
       </c>
-      <c r="H77" s="4">
+      <c r="J77" s="4">
         <v>11.88</v>
       </c>
     </row>
@@ -26475,19 +27246,29 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Уголок крепеж фигур. УКФ70-70-60-2,0-У-53  Россия</t>
         </is>
       </c>
-      <c r="E78" s="6">
+      <c r="G78" s="6">
         <v>6</v>
       </c>
-      <c r="F78" s="6">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4">
+      <c r="H78" s="6">
+        <v>0</v>
+      </c>
+      <c r="I78" s="4">
         <v>999</v>
       </c>
-      <c r="H78" s="4">
+      <c r="J78" s="4">
         <v>10.48</v>
       </c>
     </row>
@@ -26507,19 +27288,29 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Уголок крепеж фигурный УКФ 115-115-100-2,5-У-53</t>
         </is>
       </c>
-      <c r="E79" s="6">
+      <c r="G79" s="6">
         <v>9</v>
       </c>
-      <c r="F79" s="6">
-        <v>0</v>
-      </c>
-      <c r="G79" s="4">
+      <c r="H79" s="6">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4">
         <v>999</v>
       </c>
-      <c r="H79" s="4">
+      <c r="J79" s="4">
         <v>30.45</v>
       </c>
     </row>
@@ -26539,19 +27330,29 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Уголок москитной сетки пл</t>
         </is>
       </c>
-      <c r="E80" s="6">
+      <c r="G80" s="6">
         <v>10</v>
       </c>
-      <c r="F80" s="6">
-        <v>0</v>
-      </c>
-      <c r="G80" s="4">
+      <c r="H80" s="6">
+        <v>0</v>
+      </c>
+      <c r="I80" s="4">
         <v>999</v>
       </c>
-      <c r="H80" s="4">
+      <c r="J80" s="4">
         <v>2.32</v>
       </c>
     </row>
@@ -26571,19 +27372,29 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Угольник УГ-75 полимер</t>
         </is>
       </c>
-      <c r="E81" s="6">
+      <c r="G81" s="6">
         <v>50</v>
       </c>
-      <c r="F81" s="6">
+      <c r="H81" s="6">
         <v>30</v>
       </c>
-      <c r="G81" s="4">
+      <c r="I81" s="4">
         <v>999</v>
       </c>
-      <c r="H81" s="4">
+      <c r="J81" s="4">
         <v>8.15</v>
       </c>
     </row>
@@ -26603,19 +27414,29 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Цилиндр мех.ECO Z ЛПВ-70 (40*30в)</t>
         </is>
       </c>
-      <c r="E82" s="6">
+      <c r="G82" s="6">
         <v>5</v>
       </c>
-      <c r="F82" s="6">
-        <v>0</v>
-      </c>
-      <c r="G82" s="4">
+      <c r="H82" s="6">
+        <v>0</v>
+      </c>
+      <c r="I82" s="4">
         <v>999</v>
       </c>
-      <c r="H82" s="4">
+      <c r="J82" s="4">
         <v>48.6</v>
       </c>
     </row>
@@ -26635,19 +27456,29 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Цилиндр мех.ECO Z ЛПВ-80 (40*40)</t>
         </is>
       </c>
-      <c r="E83" s="6">
+      <c r="G83" s="6">
         <v>5</v>
       </c>
-      <c r="F83" s="6">
+      <c r="H83" s="6">
         <v>1</v>
       </c>
-      <c r="G83" s="4">
+      <c r="I83" s="4">
         <v>547.8</v>
       </c>
-      <c r="H83" s="4">
+      <c r="J83" s="4">
         <v>36.97</v>
       </c>
     </row>
@@ -26667,19 +27498,29 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Цилиндр мех.ECO Z ЛПВ-90 (45*45)</t>
         </is>
       </c>
-      <c r="E84" s="6">
+      <c r="G84" s="6">
         <v>4</v>
       </c>
-      <c r="F84" s="6">
-        <v>0</v>
-      </c>
-      <c r="G84" s="4">
+      <c r="H84" s="6">
+        <v>0</v>
+      </c>
+      <c r="I84" s="4">
         <v>999</v>
       </c>
-      <c r="H84" s="4">
+      <c r="J84" s="4">
         <v>37.44</v>
       </c>
     </row>
@@ -26699,19 +27540,29 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Шпингалет Аллюр G-018L бел.блистер  2шт.</t>
         </is>
       </c>
-      <c r="E85" s="6">
+      <c r="G85" s="6">
         <v>4</v>
       </c>
-      <c r="F85" s="6">
-        <v>0</v>
-      </c>
-      <c r="G85" s="4">
+      <c r="H85" s="6">
+        <v>0</v>
+      </c>
+      <c r="I85" s="4">
         <v>999</v>
       </c>
-      <c r="H85" s="4">
+      <c r="J85" s="4">
         <v>11.9</v>
       </c>
     </row>
@@ -26731,19 +27582,29 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2 замки фурнитура</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Шплинт 4,0*40</t>
         </is>
       </c>
-      <c r="E86" s="6">
+      <c r="G86" s="6">
         <v>314</v>
       </c>
-      <c r="F86" s="6">
+      <c r="H86" s="6">
         <v>14</v>
       </c>
-      <c r="G86" s="4">
+      <c r="I86" s="4">
         <v>999</v>
       </c>
-      <c r="H86" s="4">
+      <c r="J86" s="4">
         <v>8.45</v>
       </c>
     </row>

--- a/Заявки поставщикам (авторасчёт).xlsx
+++ b/Заявки поставщикам (авторасчёт).xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="К закупкам (Вариант 2)" sheetId="1" r:id="rId1"/>
+    <sheet name="К закупкам (Вариант 3)" sheetId="1" r:id="rId1"/>
     <sheet name="По поставщикам" sheetId="2" r:id="rId2"/>
     <sheet name="Сезонность и ABC-XYZ" sheetId="3" r:id="rId3"/>
     <sheet name="Неликвиды и избыток" sheetId="4" r:id="rId4"/>

--- a/Заявки поставщикам (авторасчёт).xlsx
+++ b/Заявки поставщикам (авторасчёт).xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="К закупкам (Вариант 3)" sheetId="1" r:id="rId1"/>
+    <sheet name="К закупкам (Вариант 4)" sheetId="1" r:id="rId1"/>
     <sheet name="По поставщикам" sheetId="2" r:id="rId2"/>
     <sheet name="Сезонность и ABC-XYZ" sheetId="3" r:id="rId3"/>
     <sheet name="Неликвиды и избыток" sheetId="4" r:id="rId4"/>

--- a/Заявки поставщикам (авторасчёт).xlsx
+++ b/Заявки поставщикам (авторасчёт).xlsx
@@ -124,7 +124,7 @@
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
     <col min="13" max="13" width="48" customWidth="1"/>
   </cols>
   <sheetData>
@@ -193,7 +193,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABC-XYZ</t>
+          <t xml:space="preserve">Сегмент продаж</t>
         </is>
       </c>
       <c r="M3" s="1" t="inlineStr">
@@ -250,12 +250,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.19/мес. (×0.48) → спрос 34 дн.: 0.64 + SLA 10% → запас 0.71 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.19/мес. (×0.48) → спрос 34 дн.: 0.64 + SLA 10% → запас 0.71 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -307,12 +307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.93/мес. (×1.46) → спрос 34 дн.: 1.52 + SLA 5% → запас 1.60 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.93/мес. (×1.46) → спрос 34 дн.: 1.52 + SLA 5% → запас 1.60 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -364,12 +364,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.25/мес. (×0.75) → спрос 34 дн.: 1.05 + SLA 10% → запас 1.16 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.25/мес. (×0.75) → спрос 34 дн.: 1.05 + SLA 10% → запас 1.16 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -421,12 +421,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.46/мес. (×0.42) → спрос 34 дн.: 0.68 + SLA 10% → запас 0.75 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.46/мес. (×0.42) → спрос 34 дн.: 0.68 + SLA 10% → запас 0.75 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -478,12 +478,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.35/мес. (×1.00) → спрос 34 дн.: 1.50 + SLA 10% → запас 1.65 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.35/мес. (×1.00) → спрос 34 дн.: 1.50 + SLA 10% → запас 1.65 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -535,12 +535,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.41/мес. (×0.69) → спрос 34 дн.: 1.08 + SLA 10% → запас 1.19 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 1.41/мес. (×0.69) → спрос 34 дн.: 1.08 + SLA 10% → запас 1.19 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -592,12 +592,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.58/мес. (×1.08) → спрос 34 дн.: 1.90 + SLA 12% → запас 2.12 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.58/мес. (×1.08) → спрос 34 дн.: 1.90 + SLA 12% → запас 2.12 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.29/мес. (×0.74) → спрос 34 дн.: 1.07 + SLA 10% → запас 1.18 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.29/мес. (×0.74) → спрос 34 дн.: 1.07 + SLA 10% → запас 1.18 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -706,12 +706,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.26/мес. (×0.80) → спрос 34 дн.: 1.12 + SLA 10% → запас 1.23 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.26/мес. (×0.80) → спрос 34 дн.: 1.12 + SLA 10% → запас 1.23 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -763,12 +763,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BX] База 1.23/мес. (×0.44) → спрос 34 дн.: 0.60 + SLA 11% → запас 0.66 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.23/мес. (×0.44) → спрос 34 дн.: 0.60 + SLA 11% → запас 0.66 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 1.40/мес. (×0.43) → спрос 34 дн.: 0.67 + SLA 12% → запас 0.76 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.40/мес. (×0.43) → спрос 34 дн.: 0.67 + SLA 12% → запас 0.76 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BX] База 0.92/мес. (×0.45) → спрос 34 дн.: 0.46 + SLA 11% → запас 0.51 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.92/мес. (×0.45) → спрос 34 дн.: 0.46 + SLA 11% → запас 0.51 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.95/мес. (×0.45) → спрос 34 дн.: 0.48 + SLA 10% → запас 0.53 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.95/мес. (×0.45) → спрос 34 дн.: 0.48 + SLA 10% → запас 0.53 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 1.05/мес. (×0.42) → спрос 34 дн.: 0.49 + SLA 8% → запас 0.52 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.05/мес. (×0.42) → спрос 34 дн.: 0.49 + SLA 8% → запас 0.52 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.17/мес. (×0.53) → спрос 34 дн.: 0.69 + SLA 12% → запас 0.76 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.17/мес. (×0.53) → спрос 34 дн.: 0.69 + SLA 12% → запас 0.76 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.11/мес. (×0.87) → спрос 34 дн.: 2.06 + SLA 12% → запас 2.29 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.11/мес. (×0.87) → спрос 34 дн.: 2.06 + SLA 12% → запас 2.29 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 1.26/мес. (×1.54) → спрос 34 дн.: 2.17 + SLA 10% → запас 2.37 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 1.26/мес. (×1.54) → спрос 34 дн.: 2.17 + SLA 10% → запас 2.37 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.77/мес. (×0.61) → спрос 34 дн.: 1.90 + SLA 12% → запас 2.11 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.77/мес. (×0.61) → спрос 34 дн.: 1.90 + SLA 12% → запас 2.11 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 5.12/мес. (×0.63) → спрос 34 дн.: 3.61 + SLA 12% → запас 4.02 − ост. 3 = авто 1 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 5.12/мес. (×0.63) → спрос 34 дн.: 3.61 + SLA 12% → запас 4.02 − ост. 3 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.53/мес. (×0.57) → спрос 34 дн.: 1.61 + SLA 12% → запас 1.79 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.53/мес. (×0.57) → спрос 34 дн.: 1.61 + SLA 12% → запас 1.79 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 4.22/мес. (×0.79) → спрос 34 дн.: 3.73 + SLA 12% → запас 4.20 − ост. 2 = авто 2 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 4.22/мес. (×0.79) → спрос 34 дн.: 3.73 + SLA 12% → запас 4.20 − ост. 2 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 1.62/мес. (×0.56) → спрос 34 дн.: 1.02 + SLA 12% → запас 1.14 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 1.62/мес. (×0.56) → спрос 34 дн.: 1.02 + SLA 12% → запас 1.14 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BX] База 1.81/мес. (×0.58) → спрос 34 дн.: 1.18 + SLA 11% → запас 1.31 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.81/мес. (×0.58) → спрос 34 дн.: 1.18 + SLA 11% → запас 1.31 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 0.97/мес. (×0.43) → спрос 34 дн.: 0.47 + SLA 12% → запас 0.52 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.97/мес. (×0.43) → спрос 34 дн.: 0.47 + SLA 12% → запас 0.52 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 3.79/мес. (×1.01) → спрос 34 дн.: 4.28 + SLA 12% → запас 4.77 − ост. 3 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 3.79/мес. (×1.01) → спрос 34 дн.: 4.28 + SLA 12% → запас 4.77 − ост. 3 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 7.33/мес. (×1.16) → спрос 34 дн.: 9.50 + SLA 12% → запас 10.69 − ост. 3 = авто 8 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 7.33/мес. (×1.16) → спрос 34 дн.: 9.50 + SLA 12% → запас 10.69 − ост. 3 = авто 8 ед.</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 3.29/мес. (×1.20) → спрос 34 дн.: 4.42 + SLA 12% → запас 4.93 − ост. 3 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 3.29/мес. (×1.20) → спрос 34 дн.: 4.42 + SLA 12% → запас 4.93 − ост. 3 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 5.84/мес. (×0.87) → спрос 34 дн.: 5.66 + SLA 12% → запас 6.37 − ост. 1 = авто 5 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 5.84/мес. (×0.87) → спрос 34 дн.: 5.66 + SLA 12% → запас 6.37 − ост. 1 = авто 5 ед.</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1846,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 3.53/мес. (×0.46) → спрос 34 дн.: 1.80 + SLA 12% → запас 2.01 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 3.53/мес. (×0.46) → спрос 34 дн.: 1.80 + SLA 12% → запас 2.01 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.32/мес. (×0.87) → спрос 34 дн.: 1.29 + SLA 10% → запас 1.42 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.32/мес. (×0.87) → спрос 34 дн.: 1.29 + SLA 10% → запас 1.42 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.22/мес. (×1.08) (сглажено опт-выбросов: 1) → спрос 34 дн.: 2.69 + SLA 12% → запас 3.00 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.22/мес. (×1.08) (сглажено опт-выбросов: 1) → спрос 34 дн.: 2.69 + SLA 12% → запас 3.00 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.01/мес. (×0.68) → спрос 34 дн.: 0.77 + SLA 12% → запас 0.86 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.01/мес. (×0.68) → спрос 34 дн.: 0.77 + SLA 12% → запас 0.86 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 0.76/мес. (×0.61) → спрос 34 дн.: 0.52 + SLA 8% → запас 0.56 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.76/мес. (×0.61) → спрос 34 дн.: 0.52 + SLA 8% → запас 0.56 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.81/мес. (×0.53) → спрос 34 дн.: 1.66 + SLA 12% → запас 1.85 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.81/мес. (×0.53) → спрос 34 дн.: 1.66 + SLA 12% → запас 1.85 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 4.01/мес. (×1.01) → спрос 34 дн.: 4.52 + SLA 12% → запас 5.04 − ост. 0 = авто 5 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 4.01/мес. (×1.01) → спрос 34 дн.: 4.52 + SLA 12% → запас 5.04 − ост. 0 = авто 5 ед.</t>
         </is>
       </c>
     </row>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.17/мес. (×0.41) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.98 + SLA 12% → запас 1.10 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.17/мес. (×0.41) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.98 + SLA 12% → запас 1.10 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.30/мес. (×0.40) → спрос 34 дн.: 1.04 + SLA 12% → запас 1.16 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.30/мес. (×0.40) → спрос 34 дн.: 1.04 + SLA 12% → запас 1.16 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.61/мес. (×0.34) → спрос 34 дн.: 0.61 + SLA 12% → запас 0.68 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.61/мес. (×0.34) → спрос 34 дн.: 0.61 + SLA 12% → запас 0.68 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -2416,12 +2416,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.76/мес. (×0.46) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.91 + SLA 12% → запас 1.01 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.76/мес. (×0.46) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.91 + SLA 12% → запас 1.01 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -2473,12 +2473,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.66/мес. (×0.64) → спрос 34 дн.: 1.90 + SLA 12% → запас 2.12 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 2.66/мес. (×0.64) → спрос 34 дн.: 1.90 + SLA 12% → запас 2.12 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 4.38/мес. (×0.46) → спрос 34 дн.: 2.23 + SLA 12% → запас 2.51 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 4.38/мес. (×0.46) → спрос 34 дн.: 2.23 + SLA 12% → запас 2.51 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 2.87/мес. (×0.73) → спрос 34 дн.: 2.33 + SLA 12% → запас 2.62 − ост. 1 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.87/мес. (×0.73) → спрос 34 дн.: 2.33 + SLA 12% → запас 2.62 − ост. 1 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.78/мес. (×1.07) → спрос 34 дн.: 2.12 + SLA 12% → запас 2.37 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.78/мес. (×1.07) → спрос 34 дн.: 2.12 + SLA 12% → запас 2.37 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.95/мес. (×0.97) → спрос 34 дн.: 3.20 + SLA 12% → запас 3.57 − ост. 0 = авто 4 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.95/мес. (×0.97) → спрос 34 дн.: 3.20 + SLA 12% → запас 3.57 − ост. 0 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -2758,12 +2758,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 1.40/мес. (×0.91) → спрос 34 дн.: 1.42 + SLA 10% → запас 1.55 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.40/мес. (×0.91) → спрос 34 дн.: 1.42 + SLA 10% → запас 1.55 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.00/мес. (×0.84) → спрос 34 дн.: 1.88 + SLA 12% → запас 2.10 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.00/мес. (×0.84) → спрос 34 дн.: 1.88 + SLA 12% → запас 2.10 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -2872,12 +2872,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 3.33/мес. (×0.90) → спрос 34 дн.: 3.34 + SLA 12% → запас 3.75 − ост. 3 = авто 1 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 3.33/мес. (×0.90) → спрос 34 дн.: 3.34 + SLA 12% → запас 3.75 − ост. 3 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -2929,12 +2929,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 105.34/мес. (×0.48) → спрос 34 дн.: 56.16 + SLA 12% → запас 63.18 − ост. 8 = авто 55 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 105.34/мес. (×0.48) → спрос 34 дн.: 56.16 + SLA 12% → запас 63.18 − ост. 8 = авто 55 ед.</t>
         </is>
       </c>
     </row>
@@ -2986,12 +2986,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CX</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CX] База 1.30/мес. (×0.58) → спрос 34 дн.: 0.84 + SLA 10% → запас 0.92 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 1.30/мес. (×0.58) → спрос 34 дн.: 0.84 + SLA 10% → запас 0.92 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 1.28/мес. (×0.47) → спрос 34 дн.: 0.67 + SLA 8% → запас 0.73 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 1.28/мес. (×0.47) → спрос 34 дн.: 0.67 + SLA 8% → запас 0.73 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -3100,12 +3100,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.24/мес. (×0.88) → спрос 34 дн.: 1.21 + SLA 12% → запас 1.35 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.24/мес. (×0.88) → спрос 34 дн.: 1.21 + SLA 12% → запас 1.35 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 0.74/мес. (×1.00) → спрос 34 дн.: 0.83 + SLA 12% → запас 0.93 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.74/мес. (×1.00) → спрос 34 дн.: 0.83 + SLA 12% → запас 0.93 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -3214,12 +3214,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 2.02/мес. (×0.39) → спрос 34 дн.: 0.88 + SLA 12% → запас 0.99 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.02/мес. (×0.39) → спрос 34 дн.: 0.88 + SLA 12% → запас 0.99 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.52/мес. (×0.81) → спрос 34 дн.: 1.37 + SLA 12% → запас 1.53 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.52/мес. (×0.81) → спрос 34 дн.: 1.37 + SLA 12% → запас 1.53 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -3328,12 +3328,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 2.95/мес. (×0.63) → спрос 34 дн.: 2.09 + SLA 12% → запас 2.35 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 2.95/мес. (×0.63) → спрос 34 дн.: 2.09 + SLA 12% → запас 2.35 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -3385,12 +3385,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 0.54/мес. (×1.34) → спрос 34 дн.: 0.81 + SLA 10% → запас 0.88 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.54/мес. (×1.34) → спрос 34 дн.: 0.81 + SLA 10% → запас 0.88 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 0.57/мес. (×0.97) → спрос 34 дн.: 0.62 + SLA 10% → запас 0.68 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.57/мес. (×0.97) → спрос 34 дн.: 0.62 + SLA 10% → запас 0.68 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 4.25/мес. (×0.76) → спрос 34 дн.: 3.60 + SLA 12% → запас 4.02 − ост. 1 = авто 3 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 4.25/мес. (×0.76) → спрос 34 дн.: 3.60 + SLA 12% → запас 4.02 − ост. 1 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -3556,12 +3556,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 4.69/мес. (×0.28) → спрос 34 дн.: 1.44 + SLA 12% → запас 1.61 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 4.69/мес. (×0.28) → спрос 34 дн.: 1.44 + SLA 12% → запас 1.61 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.06/мес. (×0.40) → спрос 34 дн.: 0.48 + SLA 12% → запас 0.53 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.06/мес. (×0.40) → спрос 34 дн.: 0.48 + SLA 12% → запас 0.53 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 5.53/мес. (×0.77) → спрос 34 дн.: 4.78 + SLA 12% → запас 5.38 − ост. 0 = авто 5 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 5.53/мес. (×0.77) → спрос 34 дн.: 4.78 + SLA 12% → запас 5.38 − ост. 0 = авто 5 ед.</t>
         </is>
       </c>
     </row>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 5.12/мес. (×0.66) → спрос 34 дн.: 3.79 + SLA 12% → запас 4.27 − ост. 0 = авто 4 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 5.12/мес. (×0.66) → спрос 34 дн.: 3.79 + SLA 12% → запас 4.27 − ост. 0 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -3784,12 +3784,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.99/мес. (×0.92) → спрос 34 дн.: 2.05 + SLA 10% → запас 2.25 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.99/мес. (×0.92) → спрос 34 дн.: 2.05 + SLA 10% → запас 2.25 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -3841,12 +3841,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.47/мес. (×0.92) → спрос 34 дн.: 0.48 + SLA 8% → запас 0.51 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.47/мес. (×0.92) → спрос 34 дн.: 0.48 + SLA 8% → запас 0.51 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 2.29/мес. (×0.86) → спрос 34 дн.: 2.20 + SLA 10% → запас 2.42 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.29/мес. (×0.86) → спрос 34 дн.: 2.20 + SLA 10% → запас 2.42 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -3955,12 +3955,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 3.75/мес. (×1.37) → спрос 34 дн.: 5.74 + SLA 12% → запас 6.40 − ост. 0 = авто 6 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 3.75/мес. (×1.37) → спрос 34 дн.: 5.74 + SLA 12% → запас 6.40 − ост. 0 = авто 6 ед.</t>
         </is>
       </c>
     </row>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 3.28/мес. (×0.89) → спрос 34 дн.: 3.25 + SLA 12% → запас 3.63 − ост. 0 = авто 4 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 3.28/мес. (×0.89) → спрос 34 дн.: 3.25 + SLA 12% → запас 3.63 − ост. 0 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 0.96/мес. (×0.63) → спрос 34 дн.: 0.68 + SLA 10% → запас 0.74 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.96/мес. (×0.63) → спрос 34 дн.: 0.68 + SLA 10% → запас 0.74 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.88/мес. (×1.07) → спрос 34 дн.: 3.45 + SLA 12% → запас 3.85 − ост. 0 = авто 4 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.88/мес. (×1.07) → спрос 34 дн.: 3.45 + SLA 12% → запас 3.85 − ост. 0 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 3.35/мес. (×0.84) → спрос 34 дн.: 3.13 + SLA 12% → запас 3.52 − ост. 1 = авто 3 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 3.35/мес. (×0.84) → спрос 34 дн.: 3.13 + SLA 12% → запас 3.52 − ост. 1 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 3.80/мес. (×0.96) → спрос 34 дн.: 4.06 + SLA 12% → запас 4.56 − ост. 2 = авто 3 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 3.80/мес. (×0.96) → спрос 34 дн.: 4.06 + SLA 12% → запас 4.56 − ост. 2 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -4297,12 +4297,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.56/мес. (×0.67) → спрос 34 дн.: 1.92 + SLA 12% → запас 2.15 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.56/мес. (×0.67) → спрос 34 дн.: 1.92 + SLA 12% → запас 2.15 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.73/мес. (×0.85) → спрос 34 дн.: 1.65 + SLA 12% → запас 1.84 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 1.73/мес. (×0.85) → спрос 34 дн.: 1.65 + SLA 12% → запас 1.84 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -4411,12 +4411,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.04/мес. (×0.91) → спрос 34 дн.: 2.07 + SLA 12% → запас 2.31 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 2.04/мес. (×0.91) → спрос 34 дн.: 2.07 + SLA 12% → запас 2.31 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BX] База 1.43/мес. (×0.44) → спрос 34 дн.: 0.71 + SLA 11% → запас 0.79 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.43/мес. (×0.44) → спрос 34 дн.: 0.71 + SLA 11% → запас 0.79 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -4525,12 +4525,12 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.86/мес. (×0.80) → спрос 34 дн.: 0.77 + SLA 10% → запас 0.84 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.86/мес. (×0.80) → спрос 34 дн.: 0.77 + SLA 10% → запас 0.84 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4582,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 0.67/мес. (×0.71) → спрос 34 дн.: 0.53 + SLA 8% → запас 0.57 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.67/мес. (×0.71) → спрос 34 дн.: 0.53 + SLA 8% → запас 0.57 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 1.67/мес. (×0.44) → спрос 34 дн.: 0.82 + SLA 12% → запас 0.92 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.67/мес. (×0.44) → спрос 34 дн.: 0.82 + SLA 12% → запас 0.92 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -4696,12 +4696,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 2.85/мес. (×0.21) → спрос 34 дн.: 0.66 + SLA 5% → запас 0.69 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 2.85/мес. (×0.21) → спрос 34 дн.: 0.66 + SLA 5% → запас 0.69 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 2.56/мес. (×0.86) → спрос 34 дн.: 2.45 + SLA 10% → запас 2.70 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.56/мес. (×0.86) → спрос 34 дн.: 2.45 + SLA 10% → запас 2.70 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.88/мес. (×0.61) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.59 + SLA 10% → запас 0.65 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.88/мес. (×0.61) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.59 + SLA 10% → запас 0.65 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -4867,12 +4867,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 1.28/мес. (×0.43) → спрос 34 дн.: 0.61 + SLA 12% → запас 0.68 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.28/мес. (×0.43) → спрос 34 дн.: 0.61 + SLA 12% → запас 0.68 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 1.20/мес. (×0.45) → спрос 34 дн.: 0.60 + SLA 8% → запас 0.65 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.20/мес. (×0.45) → спрос 34 дн.: 0.60 + SLA 8% → запас 0.65 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 0.87/мес. (×1.49) → спрос 34 дн.: 1.45 + SLA 12% → запас 1.62 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.87/мес. (×1.49) → спрос 34 дн.: 1.45 + SLA 12% → запас 1.62 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.99/мес. (×0.71) → спрос 34 дн.: 0.78 + SLA 10% → запас 0.86 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.99/мес. (×0.71) → спрос 34 дн.: 0.78 + SLA 10% → запас 0.86 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.51/мес. (×0.64) → спрос 34 дн.: 1.08 + SLA 12% → запас 1.20 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.51/мес. (×0.64) → спрос 34 дн.: 1.08 + SLA 12% → запас 1.20 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.19/мес. (×1.18) → спрос 34 дн.: 1.56 + SLA 10% → запас 1.72 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.19/мес. (×1.18) → спрос 34 дн.: 1.56 + SLA 10% → запас 1.72 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.52/мес. (×0.42) → спрос 34 дн.: 1.17 + SLA 12% → запас 1.30 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.52/мес. (×0.42) → спрос 34 дн.: 1.17 + SLA 12% → запас 1.30 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -5266,12 +5266,12 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 1.29/мес. (×0.39) → спрос 34 дн.: 0.57 + SLA 5% → запас 0.60 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.29/мес. (×0.39) → спрос 34 дн.: 0.57 + SLA 5% → запас 0.60 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 3.74/мес. (×0.41) → спрос 34 дн.: 1.73 + SLA 12% → запас 1.93 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 3.74/мес. (×0.41) → спрос 34 дн.: 1.73 + SLA 12% → запас 1.93 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -5380,12 +5380,12 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 3.68/мес. (×0.55) → спрос 34 дн.: 2.25 + SLA 12% → запас 2.53 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 3.68/мес. (×0.55) → спрос 34 дн.: 2.25 + SLA 12% → запас 2.53 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -5437,12 +5437,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 7.06/мес. (×0.75) → спрос 34 дн.: 5.89 + SLA 12% → запас 6.63 − ост. 2 = авто 5 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 7.06/мес. (×0.75) → спрос 34 дн.: 5.89 + SLA 12% → запас 6.63 − ост. 2 = авто 5 ед.</t>
         </is>
       </c>
     </row>
@@ -5494,12 +5494,12 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 3.45/мес. (×1.23) → спрос 34 дн.: 4.75 + SLA 12% → запас 5.29 − ост. 4 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 3.45/мес. (×1.23) → спрос 34 дн.: 4.75 + SLA 12% → запас 5.29 − ост. 4 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 2.57/мес. (×0.96) (сглажено опт-выбросов: 1) → спрос 34 дн.: 2.75 + SLA 10% → запас 3.03 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 2.57/мес. (×0.96) (сглажено опт-выбросов: 1) → спрос 34 дн.: 2.75 + SLA 10% → запас 3.03 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 3.30/мес. (×0.78) (сглажено опт-выбросов: 1) → спрос 34 дн.: 2.87 + SLA 12% → запас 3.20 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 3.30/мес. (×0.78) (сглажено опт-выбросов: 1) → спрос 34 дн.: 2.87 + SLA 12% → запас 3.20 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.36/мес. (×0.78) → спрос 34 дн.: 1.19 + SLA 12% → запас 1.32 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.36/мес. (×0.78) → спрос 34 дн.: 1.19 + SLA 12% → запас 1.32 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -5722,12 +5722,12 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.30/мес. (×1.35) → спрос 34 дн.: 1.95 + SLA 12% → запас 2.17 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 1.30/мес. (×1.35) → спрос 34 дн.: 1.95 + SLA 12% → запас 2.17 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.57/мес. (×0.87) → спрос 34 дн.: 0.56 + SLA 10% → запас 0.61 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.57/мес. (×0.87) → спрос 34 дн.: 0.56 + SLA 10% → запас 0.61 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -5836,12 +5836,12 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 2.06/мес. (×0.70) → спрос 34 дн.: 1.60 + SLA 12% → запас 1.81 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.06/мес. (×0.70) → спрос 34 дн.: 1.60 + SLA 12% → запас 1.81 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.48/мес. (×0.32) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.54 + SLA 10% → запас 0.59 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.48/мес. (×0.32) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.54 + SLA 10% → запас 0.59 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -5950,12 +5950,12 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 8.72/мес. (×0.46) → спрос 34 дн.: 4.50 + SLA 12% → запас 5.07 − ост. 4 = авто 1 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 8.72/мес. (×0.46) → спрос 34 дн.: 4.50 + SLA 12% → запас 5.07 − ост. 4 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -6007,12 +6007,12 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 1.05/мес. (×0.42) → спрос 34 дн.: 0.49 + SLA 8% → запас 0.52 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.05/мес. (×0.42) → спрос 34 дн.: 0.49 + SLA 8% → запас 0.52 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -6064,12 +6064,12 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 5.96/мес. (×0.70) → спрос 34 дн.: 4.69 + SLA 12% → запас 5.23 − ост. 2 = авто 3 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 5.96/мес. (×0.70) → спрос 34 дн.: 4.69 + SLA 12% → запас 5.23 − ост. 2 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 5.69/мес. (×0.39) → спрос 34 дн.: 2.51 + SLA 12% → запас 2.82 − ост. 2 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 5.69/мес. (×0.39) → спрос 34 дн.: 2.51 + SLA 12% → запас 2.82 − ост. 2 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -6178,12 +6178,12 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 5.36/мес. (×0.36) → спрос 34 дн.: 2.17 + SLA 12% → запас 2.45 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 5.36/мес. (×0.36) → спрос 34 дн.: 2.17 + SLA 12% → запас 2.45 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 8.06/мес. (×0.52) → спрос 34 дн.: 4.71 + SLA 12% → запас 5.30 − ост. 1 = авто 4 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 8.06/мес. (×0.52) → спрос 34 дн.: 4.71 + SLA 12% → запас 5.30 − ост. 1 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -6292,12 +6292,12 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 1.66/мес. (×0.44) → спрос 34 дн.: 0.81 + SLA 8% → запас 0.87 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.66/мес. (×0.44) → спрос 34 дн.: 0.81 + SLA 8% → запас 0.87 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 6.47/мес. (×0.42) (сглажено опт-выбросов: 1) → спрос 34 дн.: 3.01 + SLA 12% → запас 3.39 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 6.47/мес. (×0.42) (сглажено опт-выбросов: 1) → спрос 34 дн.: 3.01 + SLA 12% → запас 3.39 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -6406,12 +6406,12 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 3.66/мес. (×1.17) → спрос 34 дн.: 4.76 + SLA 12% → запас 5.31 − ост. 3 = авто 2 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 3.66/мес. (×1.17) → спрос 34 дн.: 4.76 + SLA 12% → запас 5.31 − ост. 3 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 8.64/мес. (×0.66) → спрос 34 дн.: 6.33 + SLA 12% → запас 7.13 − ост. 0 = авто 7 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 8.64/мес. (×0.66) → спрос 34 дн.: 6.33 + SLA 12% → запас 7.13 − ост. 0 = авто 7 ед.</t>
         </is>
       </c>
     </row>
@@ -6520,12 +6520,12 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.09/мес. (×0.61) (сглажено опт-выбросов: 1) → спрос 34 дн.: 1.43 + SLA 12% → запас 1.60 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.09/мес. (×0.61) (сглажено опт-выбросов: 1) → спрос 34 дн.: 1.43 + SLA 12% → запас 1.60 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 0.97/мес. (×0.57) → спрос 34 дн.: 0.62 + SLA 10% → запас 0.68 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 0.97/мес. (×0.57) → спрос 34 дн.: 0.62 + SLA 10% → запас 0.68 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 3.14/мес. (×0.92) (сглажено опт-выбросов: 1) → спрос 34 дн.: 3.23 + SLA 12% → запас 3.60 − ост. 0 = авто 4 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 3.14/мес. (×0.92) (сглажено опт-выбросов: 1) → спрос 34 дн.: 3.23 + SLA 12% → запас 3.60 − ост. 0 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.39/мес. (×1.16) → спрос 34 дн.: 0.50 + SLA 5% → запас 0.53 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.39/мес. (×1.16) → спрос 34 дн.: 0.50 + SLA 5% → запас 0.53 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -6748,12 +6748,12 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.94/мес. (×0.51) → спрос 34 дн.: 0.53 + SLA 5% → запас 0.56 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.94/мес. (×0.51) → спрос 34 дн.: 0.53 + SLA 5% → запас 0.56 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.29/мес. (×0.90) → спрос 34 дн.: 1.30 + SLA 12% → запас 1.45 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.29/мес. (×0.90) → спрос 34 дн.: 1.30 + SLA 12% → запас 1.45 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -6862,12 +6862,12 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.97/мес. (×1.16) → спрос 34 дн.: 2.55 + SLA 12% → запас 2.84 − ост. 1 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.97/мес. (×1.16) → спрос 34 дн.: 2.55 + SLA 12% → запас 2.84 − ост. 1 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.47/мес. (×0.42) → спрос 34 дн.: 0.68 + SLA 12% → запас 0.76 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.47/мес. (×0.42) → спрос 34 дн.: 0.68 + SLA 12% → запас 0.76 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -6976,12 +6976,12 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.74/мес. (×0.75) → спрос 34 дн.: 0.62 + SLA 5% → запас 0.65 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.74/мес. (×0.75) → спрос 34 дн.: 0.62 + SLA 5% → запас 0.65 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 0.62/мес. (×1.42) → спрос 34 дн.: 0.98 + SLA 8% → запас 1.06 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.62/мес. (×1.42) → спрос 34 дн.: 0.98 + SLA 8% → запас 1.06 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.36/мес. (×1.61) → спрос 34 дн.: 2.46 + SLA 12% → запас 2.74 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.36/мес. (×1.61) → спрос 34 дн.: 2.46 + SLA 12% → запас 2.74 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.95/мес. (×0.61) → спрос 34 дн.: 0.65 + SLA 10% → запас 0.71 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.95/мес. (×0.61) → спрос 34 дн.: 0.65 + SLA 10% → запас 0.71 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7204,12 +7204,12 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.17/мес. (×1.20) → спрос 34 дн.: 1.58 + SLA 12% → запас 1.76 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.17/мес. (×1.20) → спрос 34 дн.: 1.58 + SLA 12% → запас 1.76 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.94/мес. (×1.04) → спрос 34 дн.: 1.10 + SLA 10% → запас 1.21 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.94/мес. (×1.04) → спрос 34 дн.: 1.10 + SLA 10% → запас 1.21 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7318,12 +7318,12 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CX</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CX] База 0.98/мес. (×0.60) → спрос 34 дн.: 0.65 + SLA 10% → запас 0.71 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.98/мес. (×0.60) → спрос 34 дн.: 0.65 + SLA 10% → запас 0.71 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 1.00/мес. (×0.82) → спрос 34 дн.: 0.91 + SLA 8% → запас 0.99 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 1.00/мес. (×0.82) → спрос 34 дн.: 0.91 + SLA 8% → запас 0.99 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7432,12 +7432,12 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.96/мес. (×0.48) → спрос 34 дн.: 0.52 + SLA 10% → запас 0.57 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.96/мес. (×0.48) → спрос 34 дн.: 0.52 + SLA 10% → запас 0.57 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 1.33/мес. (×0.61) → спрос 34 дн.: 0.90 + SLA 8% → запас 0.97 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.33/мес. (×0.61) → спрос 34 дн.: 0.90 + SLA 8% → запас 0.97 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.72/мес. (×0.82) → спрос 34 дн.: 0.66 + SLA 8% → запас 0.71 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.72/мес. (×0.82) → спрос 34 дн.: 0.66 + SLA 8% → запас 0.71 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.04/мес. (×0.99) → спрос 34 дн.: 1.16 + SLA 10% → запас 1.27 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.04/мес. (×0.99) → спрос 34 дн.: 1.16 + SLA 10% → запас 1.27 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 0.87/мес. (×0.70) → спрос 34 дн.: 0.68 + SLA 12% → запас 0.76 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.87/мес. (×0.70) → спрос 34 дн.: 0.68 + SLA 12% → запас 0.76 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 1.20/мес. (×0.57) → спрос 34 дн.: 0.76 + SLA 8% → запас 0.82 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.20/мес. (×0.57) → спрос 34 дн.: 0.76 + SLA 8% → запас 0.82 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7774,12 +7774,12 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 0.76/мес. (×0.83) → спрос 34 дн.: 0.71 + SLA 10% → запас 0.78 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.76/мес. (×0.83) → спрос 34 дн.: 0.71 + SLA 10% → запас 0.78 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.98/мес. (×0.71) → спрос 34 дн.: 0.78 + SLA 8% → запас 0.84 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.98/мес. (×0.71) → спрос 34 дн.: 0.78 + SLA 8% → запас 0.84 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7888,12 +7888,12 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.99/мес. (×0.71) → спрос 34 дн.: 0.78 + SLA 8% → запас 0.84 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.99/мес. (×0.71) → спрос 34 дн.: 0.78 + SLA 8% → запас 0.84 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -7945,12 +7945,12 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BX</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BX] База 1.49/мес. (×0.62) → спрос 34 дн.: 1.02 + SLA 11% → запас 1.14 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.49/мес. (×0.62) → спрос 34 дн.: 1.02 + SLA 11% → запас 1.14 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -8002,12 +8002,12 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 0.44/мес. (×1.07) → спрос 34 дн.: 0.53 + SLA 8% → запас 0.56 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.44/мес. (×1.07) → спрос 34 дн.: 0.53 + SLA 8% → запас 0.56 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.54/мес. (×1.00) → спрос 34 дн.: 0.61 + SLA 10% → запас 0.67 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.54/мес. (×1.00) → спрос 34 дн.: 0.61 + SLA 10% → запас 0.67 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -8116,12 +8116,12 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.95/мес. (×0.35) → спрос 34 дн.: 0.75 + SLA 12% → запас 0.84 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.95/мес. (×0.35) → спрос 34 дн.: 0.75 + SLA 12% → запас 0.84 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.71/мес. (×0.66) (сглажено опт-выбросов: 1) → спрос 34 дн.: 1.26 + SLA 12% → запас 1.41 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.71/мес. (×0.66) (сглажено опт-выбросов: 1) → спрос 34 дн.: 1.26 + SLA 12% → запас 1.41 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -8230,12 +8230,12 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.36/мес. (×0.62) → спрос 34 дн.: 0.94 + SLA 12% → запас 1.05 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.36/мес. (×0.62) → спрос 34 дн.: 0.94 + SLA 12% → запас 1.05 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -8287,12 +8287,12 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.46/мес. (×1.19) → спрос 34 дн.: 0.61 + SLA 8% → запас 0.66 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.46/мес. (×1.19) → спрос 34 дн.: 0.61 + SLA 8% → запас 0.66 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -8344,12 +8344,12 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 0.92/мес. (×1.20) → спрос 34 дн.: 1.23 + SLA 12% → запас 1.37 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.92/мес. (×1.20) → спрос 34 дн.: 1.23 + SLA 12% → запас 1.37 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -8401,12 +8401,12 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 3.81/мес. (×0.42) → спрос 34 дн.: 1.77 + SLA 12% → запас 1.97 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 3.81/мес. (×0.42) → спрос 34 дн.: 1.77 + SLA 12% → запас 1.97 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -8458,12 +8458,12 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 3.01/мес. (×1.18) → спрос 34 дн.: 3.97 + SLA 12% → запас 4.43 − ост. 2 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 3.01/мес. (×1.18) → спрос 34 дн.: 3.97 + SLA 12% → запас 4.43 − ост. 2 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 4.73/мес. (×0.45) → спрос 34 дн.: 2.36 + SLA 12% → запас 2.63 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 4.73/мес. (×0.45) → спрос 34 дн.: 2.36 + SLA 12% → запас 2.63 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -8572,12 +8572,12 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.96/мес. (×0.43) → спрос 34 дн.: 0.46 + SLA 10% → запас 0.50 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.96/мес. (×0.43) → спрос 34 дн.: 0.46 + SLA 10% → запас 0.50 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 1.46/мес. (×1.71) → спрос 34 дн.: 2.78 + SLA 8% → запас 3.00 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.46/мес. (×1.71) → спрос 34 дн.: 2.78 + SLA 8% → запас 3.00 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -8686,12 +8686,12 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 8.01/мес. (×0.73) → спрос 34 дн.: 6.55 + SLA 12% → запас 7.37 − ост. 0 = авто 7 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 8.01/мес. (×0.73) → спрос 34 дн.: 6.55 + SLA 12% → запас 7.37 − ост. 0 = авто 7 ед.</t>
         </is>
       </c>
     </row>
@@ -8743,12 +8743,12 @@
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 7.01/мес. (×0.43) → спрос 34 дн.: 3.38 + SLA 12% → запас 3.76 − ост. 0 = авто 4 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 7.01/мес. (×0.43) → спрос 34 дн.: 3.38 + SLA 12% → запас 3.76 − ост. 0 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -8800,12 +8800,12 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.89/мес. (×0.82) → спрос 34 дн.: 0.82 + SLA 8% → запас 0.88 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.89/мес. (×0.82) → спрос 34 дн.: 0.82 + SLA 8% → запас 0.88 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -8857,12 +8857,12 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.21/мес. (×1.11) → спрос 34 дн.: 1.51 + SLA 12% → запас 1.69 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.21/мес. (×1.11) → спрос 34 дн.: 1.51 + SLA 12% → запас 1.69 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -8914,12 +8914,12 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 1.75/мес. (×0.71) → спрос 34 дн.: 1.39 + SLA 8% → запас 1.50 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.75/мес. (×0.71) → спрос 34 дн.: 1.39 + SLA 8% → запас 1.50 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 2.60/мес. (×0.68) → спрос 34 дн.: 1.98 + SLA 8% → запас 2.14 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 2.60/мес. (×0.68) → спрос 34 дн.: 1.98 + SLA 8% → запас 2.14 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.71/мес. (×0.83) → спрос 34 дн.: 1.57 + SLA 10% → запас 1.73 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 1.71/мес. (×0.83) → спрос 34 дн.: 1.57 + SLA 10% → запас 1.73 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -9085,12 +9085,12 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 2.03/мес. (×0.54) → спрос 34 дн.: 1.22 + SLA 8% → запас 1.32 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 2.03/мес. (×0.54) → спрос 34 дн.: 1.22 + SLA 8% → запас 1.32 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9142,12 +9142,12 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 0.97/мес. (×1.17) (сглажено опт-выбросов: 1) → спрос 34 дн.: 1.27 + SLA 10% → запас 1.39 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.97/мес. (×1.17) (сглажено опт-выбросов: 1) → спрос 34 дн.: 1.27 + SLA 10% → запас 1.39 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9199,12 +9199,12 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 1.02/мес. (×0.56) → спрос 34 дн.: 0.64 + SLA 5% → запас 0.67 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.02/мес. (×0.56) → спрос 34 дн.: 0.64 + SLA 5% → запас 0.67 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9256,12 +9256,12 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 1.56/мес. (×0.60) → спрос 34 дн.: 1.05 + SLA 12% → запас 1.18 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.56/мес. (×0.60) → спрос 34 дн.: 1.05 + SLA 12% → запас 1.18 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9313,12 +9313,12 @@
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.91/мес. (×0.47) → спрос 34 дн.: 0.48 + SLA 8% → запас 0.52 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.91/мес. (×0.47) → спрос 34 дн.: 0.48 + SLA 8% → запас 0.52 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9370,12 +9370,12 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 2.24/мес. (×0.26) → спрос 34 дн.: 0.65 + SLA 8% → запас 0.71 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 2.24/мес. (×0.26) → спрос 34 дн.: 0.65 + SLA 8% → запас 0.71 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.49/мес. (×0.41) → спрос 34 дн.: 0.68 + SLA 12% → запас 0.76 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.49/мес. (×0.41) → спрос 34 дн.: 0.68 + SLA 12% → запас 0.76 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 2.26/мес. (×0.55) → спрос 34 дн.: 1.38 + SLA 10% → запас 1.52 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 2.26/мес. (×0.55) → спрос 34 дн.: 1.38 + SLA 10% → запас 1.52 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -9541,12 +9541,12 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 2.00/мес. (×1.37) → спрос 34 дн.: 3.06 + SLA 10% → запас 3.37 − ост. 1 = авто 2 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 2.00/мес. (×1.37) → спрос 34 дн.: 3.06 + SLA 10% → запас 3.37 − ост. 1 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -9598,12 +9598,12 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 2.27/мес. (×1.20) → спрос 34 дн.: 3.04 + SLA 10% → запас 3.34 − ост. 1 = авто 2 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 2.27/мес. (×1.20) → спрос 34 дн.: 3.04 + SLA 10% → запас 3.34 − ост. 1 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -9655,12 +9655,12 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.90/мес. (×0.45) → спрос 34 дн.: 0.96 + SLA 10% → запас 1.06 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.90/мес. (×0.45) → спрос 34 дн.: 0.96 + SLA 10% → запас 1.06 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9712,12 +9712,12 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BX] База 1.89/мес. (×0.45) → спрос 34 дн.: 0.95 + SLA 11% → запас 1.06 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.89/мес. (×0.45) → спрос 34 дн.: 0.95 + SLA 11% → запас 1.06 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9769,12 +9769,12 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.90/мес. (×0.45) → спрос 34 дн.: 0.96 + SLA 10% → запас 1.06 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.90/мес. (×0.45) → спрос 34 дн.: 0.96 + SLA 10% → запас 1.06 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9826,12 +9826,12 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.74/мес. (×0.97) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.80 + SLA 10% → запас 0.88 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.74/мес. (×0.97) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.80 + SLA 10% → запас 0.88 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9883,12 +9883,12 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 0.69/мес. (×0.70) → спрос 34 дн.: 0.54 + SLA 10% → запас 0.60 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.69/мес. (×0.70) → спрос 34 дн.: 0.54 + SLA 10% → запас 0.60 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.11/мес. (×0.70) → спрос 34 дн.: 0.86 + SLA 12% → запас 0.96 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.11/мес. (×0.70) → спрос 34 дн.: 0.86 + SLA 12% → запас 0.96 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -9997,12 +9997,12 @@
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.53/мес. (×0.54) → спрос 34 дн.: 0.93 + SLA 12% → запас 1.04 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.53/мес. (×0.54) → спрос 34 дн.: 0.93 + SLA 12% → запас 1.04 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -10054,12 +10054,12 @@
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 15.16/мес. (×0.58) → спрос 34 дн.: 9.85 + SLA 10% → запас 10.78 − ост. 0 = авто 11 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 15.16/мес. (×0.58) → спрос 34 дн.: 9.85 + SLA 10% → запас 10.78 − ост. 0 = авто 11 ед.</t>
         </is>
       </c>
     </row>
@@ -10111,12 +10111,12 @@
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.63/мес. (×0.94) → спрос 34 дн.: 0.66 + SLA 5% → запас 0.69 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.63/мес. (×0.94) → спрос 34 дн.: 0.66 + SLA 5% → запас 0.69 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -10168,12 +10168,12 @@
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 1.11/мес. (×0.79) → спрос 34 дн.: 0.98 + SLA 8% → запас 1.06 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 1.11/мес. (×0.79) → спрос 34 дн.: 0.98 + SLA 8% → запас 1.06 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 2.30/мес. (×0.73) → спрос 34 дн.: 1.88 + SLA 10% → запас 2.07 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.30/мес. (×0.73) → спрос 34 дн.: 1.88 + SLA 10% → запас 2.07 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -10282,12 +10282,12 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.13/мес. (×1.21) → спрос 34 дн.: 1.52 + SLA 10% → запас 1.68 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.13/мес. (×1.21) → спрос 34 дн.: 1.52 + SLA 10% → запас 1.68 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -10339,12 +10339,12 @@
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.68/мес. (×0.63) → спрос 34 дн.: 0.48 + SLA 8% → запас 0.52 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.68/мес. (×0.63) → спрос 34 дн.: 0.48 + SLA 8% → запас 0.52 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -10396,12 +10396,12 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.72/мес. (×1.32) → спрос 34 дн.: 1.06 + SLA 8% → запас 1.14 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.72/мес. (×1.32) → спрос 34 дн.: 1.06 + SLA 8% → запас 1.14 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -10453,12 +10453,12 @@
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.75/мес. (×1.60) → спрос 34 дн.: 1.34 + SLA 8% → запас 1.44 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.75/мес. (×1.60) → спрос 34 дн.: 1.34 + SLA 8% → запас 1.44 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.91/мес. (×1.67) → спрос 34 дн.: 1.70 + SLA 8% → запас 1.83 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.91/мес. (×1.67) → спрос 34 дн.: 1.70 + SLA 8% → запас 1.83 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -10567,12 +10567,12 @@
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CX</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CX] База 0.90/мес. (×0.80) → спрос 34 дн.: 0.81 + SLA 10% → запас 0.88 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.90/мес. (×0.80) → спрос 34 дн.: 0.81 + SLA 10% → запас 0.88 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -10624,12 +10624,12 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CX</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CX] База 1.39/мес. (×1.01) → спрос 34 дн.: 1.57 + SLA 10% → запас 1.72 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 1.39/мес. (×1.01) → спрос 34 дн.: 1.57 + SLA 10% → запас 1.72 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 0.59/мес. (×1.04) → спрос 34 дн.: 0.68 + SLA 10% → запас 0.74 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.59/мес. (×1.04) → спрос 34 дн.: 0.68 + SLA 10% → запас 0.74 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -10738,12 +10738,12 @@
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BX</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BX] База 0.71/мес. (×0.96) → спрос 34 дн.: 0.76 + SLA 11% → запас 0.84 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.71/мес. (×0.96) → спрос 34 дн.: 0.76 + SLA 11% → запас 0.84 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -10795,12 +10795,12 @@
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.01/мес. (×0.53) → спрос 34 дн.: 0.60 + SLA 12% → запас 0.67 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.01/мес. (×0.53) → спрос 34 дн.: 0.60 + SLA 12% → запас 0.67 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -10852,12 +10852,12 @@
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 0.68/мес. (×0.79) → спрос 34 дн.: 0.60 + SLA 12% → запас 0.66 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.68/мес. (×0.79) → спрос 34 дн.: 0.60 + SLA 12% → запас 0.66 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 0.40/мес. (×1.49) → спрос 34 дн.: 0.67 + SLA 12% → запас 0.75 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.40/мес. (×1.49) → спрос 34 дн.: 0.67 + SLA 12% → запас 0.75 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -10966,12 +10966,12 @@
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 0.67/мес. (×0.82) → спрос 34 дн.: 0.62 + SLA 12% → запас 0.69 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.67/мес. (×0.82) → спрос 34 дн.: 0.62 + SLA 12% → запас 0.69 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -11023,12 +11023,12 @@
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 0.83/мес. (×1.55) → спрос 34 дн.: 1.45 + SLA 12% → запас 1.61 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.83/мес. (×1.55) → спрос 34 дн.: 1.45 + SLA 12% → запас 1.61 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 0.26/мес. (×1.67) → спрос 34 дн.: 0.48 + SLA 8% → запас 0.51 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.26/мес. (×1.67) → спрос 34 дн.: 0.48 + SLA 8% → запас 0.51 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.45/мес. (×1.29) → спрос 34 дн.: 0.65 + SLA 5% → запас 0.68 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.45/мес. (×1.29) → спрос 34 дн.: 0.65 + SLA 5% → запас 0.68 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -11194,12 +11194,12 @@
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.30/мес. (×2.08) → спрос 34 дн.: 0.70 + SLA 5% → запас 0.73 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.30/мес. (×2.08) → спрос 34 дн.: 0.70 + SLA 5% → запас 0.73 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -11251,12 +11251,12 @@
       </c>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CX] База 2.11/мес. (×1.04) → спрос 34 дн.: 2.46 + SLA 10% → запас 2.70 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.11/мес. (×1.04) → спрос 34 дн.: 2.46 + SLA 10% → запас 2.70 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -11308,12 +11308,12 @@
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 2.10/мес. (×0.87) → спрос 34 дн.: 2.03 + SLA 8% → запас 2.19 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.10/мес. (×0.87) → спрос 34 дн.: 2.03 + SLA 8% → запас 2.19 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -11365,12 +11365,12 @@
       </c>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 2.09/мес. (×0.78) → спрос 34 дн.: 1.81 + SLA 10% → запас 1.99 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.09/мес. (×0.78) → спрос 34 дн.: 1.81 + SLA 10% → запас 1.99 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 2.10/мес. (×0.87) → спрос 34 дн.: 2.03 + SLA 10% → запас 2.23 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.10/мес. (×0.87) → спрос 34 дн.: 2.03 + SLA 10% → запас 2.23 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -11479,12 +11479,12 @@
       </c>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.72/мес. (×1.17) → спрос 34 дн.: 0.94 + SLA 5% → запас 0.98 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.72/мес. (×1.17) → спрос 34 дн.: 0.94 + SLA 5% → запас 0.98 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 0.80/мес. (×1.56) (сглажено опт-выбросов: 1) → спрос 34 дн.: 1.39 + SLA 8% → запас 1.49 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.80/мес. (×1.56) (сглажено опт-выбросов: 1) → спрос 34 дн.: 1.39 + SLA 8% → запас 1.49 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -11593,12 +11593,12 @@
       </c>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.96/мес. (×1.98) → спрос 34 дн.: 2.12 + SLA 10% → запас 2.33 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.96/мес. (×1.98) → спрос 34 дн.: 2.12 + SLA 10% → запас 2.33 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -11650,12 +11650,12 @@
       </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.20/мес. (×1.14) → спрос 34 дн.: 1.52 + SLA 12% → запас 1.70 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 1.20/мес. (×1.14) → спрос 34 дн.: 1.52 + SLA 12% → запас 1.70 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -11707,12 +11707,12 @@
       </c>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.61/мес. (×0.78) → спрос 34 дн.: 0.53 + SLA 10% → запас 0.58 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.61/мес. (×0.78) → спрос 34 дн.: 0.53 + SLA 10% → запас 0.58 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -11764,12 +11764,12 @@
       </c>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.64/мес. (×1.11) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.79 + SLA 5% → запас 0.83 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.64/мес. (×1.11) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.79 + SLA 5% → запас 0.83 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -11821,12 +11821,12 @@
       </c>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.37/мес. (×1.32) → спрос 34 дн.: 0.55 + SLA 5% → запас 0.58 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.37/мес. (×1.32) → спрос 34 дн.: 0.55 + SLA 5% → запас 0.58 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -11878,12 +11878,12 @@
       </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 1.13/мес. (×0.48) → спрос 34 дн.: 0.60 + SLA 12% → запас 0.67 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.13/мес. (×0.48) → спрос 34 дн.: 0.60 + SLA 12% → запас 0.67 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -11935,12 +11935,12 @@
       </c>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 1.02/мес. (×0.77) → спрос 34 дн.: 0.88 + SLA 8% → запас 0.94 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.02/мес. (×0.77) → спрос 34 дн.: 0.88 + SLA 8% → запас 0.94 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BX] База 1.34/мес. (×1.27) → спрос 34 дн.: 1.90 + SLA 11% → запас 2.11 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.34/мес. (×1.27) → спрос 34 дн.: 1.90 + SLA 11% → запас 2.11 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -12049,12 +12049,12 @@
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 0.84/мес. (×0.78) → спрос 34 дн.: 0.72 + SLA 10% → запас 0.79 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.84/мес. (×0.78) → спрос 34 дн.: 0.72 + SLA 10% → запас 0.79 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.76/мес. (×2.45) (сглажено опт-выбросов: 1) → спрос 34 дн.: 2.07 + SLA 5% → запас 2.18 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.76/мес. (×2.45) (сглажено опт-выбросов: 1) → спрос 34 дн.: 2.07 + SLA 5% → запас 2.18 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -12163,12 +12163,12 @@
       </c>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.55/мес. (×0.80) → спрос 34 дн.: 0.49 + SLA 8% → запас 0.53 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.55/мес. (×0.80) → спрос 34 дн.: 0.49 + SLA 8% → запас 0.53 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -12220,12 +12220,12 @@
       </c>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 2.07/мес. (×0.66) → спрос 34 дн.: 1.54 + SLA 8% → запас 1.66 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 2.07/мес. (×0.66) → спрос 34 дн.: 1.54 + SLA 8% → запас 1.66 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -12277,12 +12277,12 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.68/мес. (×1.52) → спрос 34 дн.: 1.16 + SLA 8% → запас 1.25 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.68/мес. (×1.52) → спрос 34 дн.: 1.16 + SLA 8% → запас 1.25 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -12334,12 +12334,12 @@
       </c>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 0.91/мес. (×0.68) → спрос 34 дн.: 0.69 + SLA 12% → запас 0.77 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.91/мес. (×0.68) → спрос 34 дн.: 0.69 + SLA 12% → запас 0.77 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -12391,12 +12391,12 @@
       </c>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 0.70/мес. (×0.61) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.48 + SLA 8% → запас 0.51 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.70/мес. (×0.61) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.48 + SLA 8% → запас 0.51 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -12448,12 +12448,12 @@
       </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 3.07/мес. (×0.40) → спрос 34 дн.: 1.38 + SLA 10% → запас 1.52 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 3.07/мес. (×0.40) → спрос 34 дн.: 1.38 + SLA 10% → запас 1.52 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -12505,12 +12505,12 @@
       </c>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 1.27/мес. (×2.62) → спрос 34 дн.: 3.71 + SLA 5% → запас 3.90 − ост. 0 = авто 4 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.27/мес. (×2.62) → спрос 34 дн.: 3.71 + SLA 5% → запас 3.90 − ост. 0 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 19.85/мес. (×0.67) → спрос 34 дн.: 14.92 + SLA 8% → запас 16.11 − ост. 0 = авто 16 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 19.85/мес. (×0.67) → спрос 34 дн.: 14.92 + SLA 8% → запас 16.11 − ост. 0 = авто 16 ед.</t>
         </is>
       </c>
     </row>
@@ -12619,12 +12619,12 @@
       </c>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 24.14/мес. (×1.24) → спрос 34 дн.: 33.50 + SLA 10% → запас 36.85 − ост. 22 = авто 15 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 24.14/мес. (×1.24) → спрос 34 дн.: 33.50 + SLA 10% → запас 36.85 − ост. 22 = авто 15 ед.</t>
         </is>
       </c>
     </row>
@@ -12676,12 +12676,12 @@
       </c>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 9.29/мес. (×0.84) → спрос 34 дн.: 8.74 + SLA 10% → запас 9.61 − ост. 0 = авто 10 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 9.29/мес. (×0.84) → спрос 34 дн.: 8.74 + SLA 10% → запас 9.61 − ост. 0 = авто 10 ед.</t>
         </is>
       </c>
     </row>
@@ -12733,12 +12733,12 @@
       </c>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 6.36/мес. (×0.32) → спрос 34 дн.: 2.25 + SLA 10% → запас 2.47 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 6.36/мес. (×0.32) → спрос 34 дн.: 2.25 + SLA 10% → запас 2.47 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -12790,12 +12790,12 @@
       </c>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.53/мес. (×1.29) → спрос 34 дн.: 0.77 + SLA 5% → запас 0.81 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.53/мес. (×1.29) → спрос 34 дн.: 0.77 + SLA 5% → запас 0.81 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -12847,12 +12847,12 @@
       </c>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BX] База 4.32/мес. (×0.54) → спрос 34 дн.: 2.60 + SLA 11% → запас 2.89 − ост. 1 = авто 2 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 4.32/мес. (×0.54) → спрос 34 дн.: 2.60 + SLA 11% → запас 2.89 − ост. 1 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -12904,12 +12904,12 @@
       </c>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.55/мес. (×2.11) → спрос 34 дн.: 3.66 + SLA 10% → запас 4.03 − ост. 1 = авто 3 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.55/мес. (×2.11) → спрос 34 дн.: 3.66 + SLA 10% → запас 4.03 − ост. 1 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -12961,12 +12961,12 @@
       </c>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.35/мес. (×1.24) → спрос 34 дн.: 0.49 + SLA 5% → запас 0.51 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.35/мес. (×1.24) → спрос 34 дн.: 0.49 + SLA 5% → запас 0.51 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -13018,12 +13018,12 @@
       </c>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 4.96/мес. (×0.98) → спрос 34 дн.: 5.42 + SLA 10% → запас 5.96 − ост. 0 = авто 6 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 4.96/мес. (×0.98) → спрос 34 дн.: 5.42 + SLA 10% → запас 5.96 − ост. 0 = авто 6 ед.</t>
         </is>
       </c>
     </row>
@@ -13075,12 +13075,12 @@
       </c>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CX] База 1.74/мес. (×0.88) → спрос 34 дн.: 1.71 + SLA 10% → запас 1.87 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.74/мес. (×0.88) → спрос 34 дн.: 1.71 + SLA 10% → запас 1.87 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -13132,12 +13132,12 @@
       </c>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.48/мес. (×1.32) → спрос 34 дн.: 0.71 + SLA 5% → запас 0.74 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.48/мес. (×1.32) → спрос 34 дн.: 0.71 + SLA 5% → запас 0.74 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -13189,12 +13189,12 @@
       </c>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 6.44/мес. (×1.54) → спрос 34 дн.: 11.09 + SLA 10% → запас 12.20 − ост. 11 = авто 1 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 6.44/мес. (×1.54) → спрос 34 дн.: 11.09 + SLA 10% → запас 12.20 − ост. 11 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 2.04/мес. (×1.10) → спрос 34 дн.: 2.50 + SLA 8% → запас 2.70 − ост. 2 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.04/мес. (×1.10) → спрос 34 дн.: 2.50 + SLA 8% → запас 2.70 − ост. 2 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -13303,12 +13303,12 @@
       </c>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 1.74/мес. (×0.79) → спрос 34 дн.: 1.53 + SLA 8% → запас 1.66 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 1.74/мес. (×0.79) → спрос 34 дн.: 1.53 + SLA 8% → запас 1.66 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -13360,12 +13360,12 @@
       </c>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 2.09/мес. (×0.78) → спрос 34 дн.: 1.81 + SLA 8% → запас 1.95 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.09/мес. (×0.78) → спрос 34 дн.: 1.81 + SLA 8% → запас 1.95 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -13417,12 +13417,12 @@
       </c>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.52/мес. (×1.69) → спрос 34 дн.: 0.99 + SLA 5% → запас 1.03 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.52/мес. (×1.69) → спрос 34 дн.: 0.99 + SLA 5% → запас 1.03 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -13474,12 +13474,12 @@
       </c>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 1.08/мес. (×0.49) → спрос 34 дн.: 0.60 + SLA 5% → запас 0.62 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.08/мес. (×0.49) → спрос 34 дн.: 0.60 + SLA 5% → запас 0.62 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -13531,12 +13531,12 @@
       </c>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.87/мес. (×0.80) → спрос 34 дн.: 0.79 + SLA 5% → запас 0.82 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.87/мес. (×0.80) → спрос 34 дн.: 0.79 + SLA 5% → запас 0.82 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -13588,12 +13588,12 @@
       </c>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.67/мес. (×0.83) → спрос 34 дн.: 0.63 + SLA 5% → запас 0.66 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.67/мес. (×0.83) → спрос 34 дн.: 0.63 + SLA 5% → запас 0.66 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -13645,12 +13645,12 @@
       </c>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.70/мес. (×1.87) → спрос 34 дн.: 1.46 + SLA 8% → запас 1.57 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.70/мес. (×1.87) → спрос 34 дн.: 1.46 + SLA 8% → запас 1.57 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.68/мес. (×0.92) → спрос 34 дн.: 0.70 + SLA 5% → запас 0.73 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.68/мес. (×0.92) → спрос 34 дн.: 0.70 + SLA 5% → запас 0.73 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -13759,12 +13759,12 @@
       </c>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.44/мес. (×1.42) → спрос 34 дн.: 0.70 + SLA 8% → запас 0.75 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.44/мес. (×1.42) → спрос 34 дн.: 0.70 + SLA 8% → запас 0.75 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -13816,12 +13816,12 @@
       </c>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.92/мес. (×0.81) → спрос 34 дн.: 0.83 + SLA 8% → запас 0.90 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.92/мес. (×0.81) → спрос 34 дн.: 0.83 + SLA 8% → запас 0.90 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.45/мес. (×2.24) → спрос 34 дн.: 1.12 + SLA 5% → запас 1.17 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.45/мес. (×2.24) → спрос 34 дн.: 1.12 + SLA 5% → запас 1.17 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -13930,12 +13930,12 @@
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.54/мес. (×1.79) → спрос 34 дн.: 1.08 + SLA 5% → запас 1.14 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.54/мес. (×1.79) → спрос 34 дн.: 1.08 + SLA 5% → запас 1.14 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -13987,12 +13987,12 @@
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 1.25/мес. (×1.70) → спрос 34 дн.: 2.38 + SLA 8% → запас 2.57 − ост. 1 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.25/мес. (×1.70) → спрос 34 дн.: 2.38 + SLA 8% → запас 2.57 − ост. 1 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 3.66/мес. (×0.44) → спрос 34 дн.: 1.78 + SLA 10% → запас 1.95 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 3.66/мес. (×0.44) → спрос 34 дн.: 1.78 + SLA 10% → запас 1.95 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -14101,12 +14101,12 @@
       </c>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 2.64/мес. (×0.87) → спрос 34 дн.: 2.57 + SLA 10% → запас 2.82 − ост. 1 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.64/мес. (×0.87) → спрос 34 дн.: 2.57 + SLA 10% → запас 2.82 − ост. 1 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M248" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 1.32/мес. (×0.69) → спрос 34 дн.: 1.02 + SLA 8% → запас 1.09 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 1.32/мес. (×0.69) → спрос 34 дн.: 1.02 + SLA 8% → запас 1.09 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -14215,12 +14215,12 @@
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 2.55/мес. (×1.03) (сглажено опт-выбросов: 1) → спрос 34 дн.: 2.95 + SLA 8% → запас 3.17 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.55/мес. (×1.03) (сглажено опт-выбросов: 1) → спрос 34 дн.: 2.95 + SLA 8% → запас 3.17 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -14272,12 +14272,12 @@
       </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.83/мес. (×1.19) → спрос 34 дн.: 1.10 + SLA 5% → запас 1.15 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.83/мес. (×1.19) → спрос 34 дн.: 1.10 + SLA 5% → запас 1.15 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -14329,12 +14329,12 @@
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 3.51/мес. (×1.19) → спрос 34 дн.: 4.67 + SLA 10% → запас 5.12 − ост. 0 = авто 5 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 3.51/мес. (×1.19) → спрос 34 дн.: 4.67 + SLA 10% → запас 5.12 − ост. 0 = авто 5 ед.</t>
         </is>
       </c>
     </row>
@@ -14386,12 +14386,12 @@
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 3.27/мес. (×0.71) → спрос 34 дн.: 2.61 + SLA 12% → запас 2.91 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 3.27/мес. (×0.71) → спрос 34 дн.: 2.61 + SLA 12% → запас 2.91 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -14443,12 +14443,12 @@
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 2.79/мес. (×0.62) → спрос 34 дн.: 1.94 + SLA 10% → запас 2.13 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.79/мес. (×0.62) → спрос 34 дн.: 1.94 + SLA 10% → запас 2.13 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 1.77/мес. (×0.46) → спрос 34 дн.: 0.90 + SLA 10% → запас 0.99 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 1.77/мес. (×0.46) → спрос 34 дн.: 0.90 + SLA 10% → запас 0.99 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -14557,12 +14557,12 @@
       </c>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M255" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 3.43/мес. (×1.97) → спрос 34 дн.: 7.55 + SLA 10% → запас 8.27 − ост. 4 = авто 4 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 3.43/мес. (×1.97) → спрос 34 дн.: 7.55 + SLA 10% → запас 8.27 − ост. 4 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -14614,12 +14614,12 @@
       </c>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M256" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 1.91/мес. (×0.39) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.83 + SLA 10% → запас 0.91 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 1.91/мес. (×0.39) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.83 + SLA 10% → запас 0.91 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -14671,12 +14671,12 @@
       </c>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 10.44/мес. (×0.64) → спрос 34 дн.: 7.48 + SLA 12% → запас 8.34 − ост. 0 = авто 8 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 10.44/мес. (×0.64) → спрос 34 дн.: 7.48 + SLA 12% → запас 8.34 − ост. 0 = авто 8 ед.</t>
         </is>
       </c>
     </row>
@@ -14728,12 +14728,12 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BX] База 3.51/мес. (×1.03) → спрос 34 дн.: 4.02 + SLA 11% → запас 4.46 − ост. 0 = авто 4 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 3.51/мес. (×1.03) → спрос 34 дн.: 4.02 + SLA 11% → запас 4.46 − ост. 0 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -14785,12 +14785,12 @@
       </c>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.47/мес. (×1.06) → спрос 34 дн.: 0.56 + SLA 5% → запас 0.59 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.47/мес. (×1.06) → спрос 34 дн.: 0.56 + SLA 5% → запас 0.59 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -14842,12 +14842,12 @@
       </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 2.26/мес. (×0.64) → спрос 34 дн.: 1.61 + SLA 10% → запас 1.77 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 2.26/мес. (×0.64) → спрос 34 дн.: 1.61 + SLA 10% → запас 1.77 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -14899,12 +14899,12 @@
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 3.21/мес. (×1.27) → спрос 34 дн.: 4.55 + SLA 10% → запас 5.01 − ост. 0 = авто 5 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 3.21/мес. (×1.27) → спрос 34 дн.: 4.55 + SLA 10% → запас 5.01 − ост. 0 = авто 5 ед.</t>
         </is>
       </c>
     </row>
@@ -14956,12 +14956,12 @@
       </c>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 5.00/мес. (×0.72) (сглажено опт-выбросов: 1) → спрос 34 дн.: 4.00 + SLA 10% → запас 4.41 − ост. 2 = авто 2 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 5.00/мес. (×0.72) (сглажено опт-выбросов: 1) → спрос 34 дн.: 4.00 + SLA 10% → запас 4.41 − ост. 2 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -15013,12 +15013,12 @@
       </c>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 5.40/мес. (×1.30) (сглажено опт-выбросов: 1) → спрос 34 дн.: 7.82 + SLA 8% → запас 8.45 − ост. 0 = авто 8 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 5.40/мес. (×1.30) (сглажено опт-выбросов: 1) → спрос 34 дн.: 7.82 + SLA 8% → запас 8.45 − ост. 0 = авто 8 ед.</t>
         </is>
       </c>
     </row>
@@ -15070,12 +15070,12 @@
       </c>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.52/мес. (×1.20) → спрос 34 дн.: 0.70 + SLA 5% → запас 0.73 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 0.52/мес. (×1.20) → спрос 34 дн.: 0.70 + SLA 5% → запас 0.73 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -15127,12 +15127,12 @@
       </c>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.49/мес. (×1.30) → спрос 34 дн.: 0.71 + SLA 5% → запас 0.75 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.49/мес. (×1.30) → спрос 34 дн.: 0.71 + SLA 5% → запас 0.75 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -15184,12 +15184,12 @@
       </c>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CX] База 2.09/мес. (×0.87) → спрос 34 дн.: 2.02 + SLA 10% → запас 2.21 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.09/мес. (×0.87) → спрос 34 дн.: 2.02 + SLA 10% → запас 2.21 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -15241,12 +15241,12 @@
       </c>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.89/мес. (×1.47) → спрос 34 дн.: 3.11 + SLA 10% → запас 3.42 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.89/мес. (×1.47) → спрос 34 дн.: 3.11 + SLA 10% → запас 3.42 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -15298,12 +15298,12 @@
       </c>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 3.10/мес. (×1.78) → спрос 34 дн.: 6.16 + SLA 10% → запас 6.78 − ост. 0 = авто 7 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 3.10/мес. (×1.78) → спрос 34 дн.: 6.16 + SLA 10% → запас 6.78 − ост. 0 = авто 7 ед.</t>
         </is>
       </c>
     </row>
@@ -15355,12 +15355,12 @@
       </c>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 2.31/мес. (×2.43) (сглажено опт-выбросов: 1) → спрос 34 дн.: 6.28 + SLA 10% → запас 6.91 − ост. 5 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.31/мес. (×2.43) (сглажено опт-выбросов: 1) → спрос 34 дн.: 6.28 + SLA 10% → запас 6.91 − ост. 5 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -15412,12 +15412,12 @@
       </c>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 3.80/мес. (×0.59) → спрос 34 дн.: 2.52 + SLA 10% → запас 2.77 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 3.80/мес. (×0.59) → спрос 34 дн.: 2.52 + SLA 10% → запас 2.77 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -15469,12 +15469,12 @@
       </c>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 5.36/мес. (×2.19) → спрос 34 дн.: 13.12 + SLA 10% → запас 14.43 − ост. 6 = авто 8 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 5.36/мес. (×2.19) → спрос 34 дн.: 13.12 + SLA 10% → запас 14.43 − ост. 6 = авто 8 ед.</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BX] База 9.70/мес. (×0.97) → спрос 34 дн.: 10.54 + SLA 11% → запас 11.70 − ост. 0 = авто 12 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 9.70/мес. (×0.97) → спрос 34 дн.: 10.54 + SLA 11% → запас 11.70 − ост. 0 = авто 12 ед.</t>
         </is>
       </c>
     </row>
@@ -15583,12 +15583,12 @@
       </c>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 2.82/мес. (×0.84) → спрос 34 дн.: 2.63 + SLA 8% → запас 2.84 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.82/мес. (×0.84) → спрос 34 дн.: 2.63 + SLA 8% → запас 2.84 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -15640,12 +15640,12 @@
       </c>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 3.01/мес. (×0.63) → спрос 34 дн.: 2.12 + SLA 10% → запас 2.33 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 3.01/мес. (×0.63) → спрос 34 дн.: 2.12 + SLA 10% → запас 2.33 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -15697,12 +15697,12 @@
       </c>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M275" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 1.69/мес. (×0.73) → спрос 34 дн.: 1.38 + SLA 8% → запас 1.49 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.69/мес. (×0.73) → спрос 34 дн.: 1.38 + SLA 8% → запас 1.49 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -15754,12 +15754,12 @@
       </c>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 4.66/мес. (×0.47) → спрос 34 дн.: 2.47 + SLA 10% → запас 2.72 − ост. 1 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 4.66/мес. (×0.47) → спрос 34 дн.: 2.47 + SLA 10% → запас 2.72 − ост. 1 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -15811,12 +15811,12 @@
       </c>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M277" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 1.40/мес. (×0.63) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.99 + SLA 8% → запас 1.06 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 1.40/мес. (×0.63) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.99 + SLA 8% → запас 1.06 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -15868,12 +15868,12 @@
       </c>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 3.67/мес. (×1.91) → спрос 34 дн.: 7.85 + SLA 10% → запас 8.64 − ост. 0 = авто 9 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 3.67/мес. (×1.91) → спрос 34 дн.: 7.85 + SLA 10% → запас 8.64 − ост. 0 = авто 9 ед.</t>
         </is>
       </c>
     </row>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 1.60/мес. (×0.90) → спрос 34 дн.: 1.61 + SLA 8% → запас 1.74 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.60/мес. (×0.90) → спрос 34 дн.: 1.61 + SLA 8% → запас 1.74 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -15982,12 +15982,12 @@
       </c>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M280" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 0.71/мес. (×1.22) → спрос 34 дн.: 0.96 + SLA 8% → запас 1.04 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.71/мес. (×1.22) → спрос 34 дн.: 0.96 + SLA 8% → запас 1.04 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -16039,12 +16039,12 @@
       </c>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 1.18/мес. (×0.58) → спрос 34 дн.: 0.77 + SLA 5% → запас 0.81 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.18/мес. (×0.58) → спрос 34 дн.: 0.77 + SLA 5% → запас 0.81 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -16096,12 +16096,12 @@
       </c>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M282" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 1.71/мес. (×0.29) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.56 + SLA 10% → запас 0.61 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 1.71/мес. (×0.29) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.56 + SLA 10% → запас 0.61 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -16153,12 +16153,12 @@
       </c>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M283" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.78/мес. (×0.97) → спрос 34 дн.: 0.85 + SLA 8% → запас 0.92 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.78/мес. (×0.97) → спрос 34 дн.: 0.85 + SLA 8% → запас 0.92 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -16210,12 +16210,12 @@
       </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.75/мес. (×0.70) → спрос 34 дн.: 0.59 + SLA 5% → запас 0.62 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.75/мес. (×0.70) → спрос 34 дн.: 0.59 + SLA 5% → запас 0.62 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -16267,12 +16267,12 @@
       </c>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 1.12/мес. (×0.86) → спрос 34 дн.: 1.08 + SLA 5% → запас 1.13 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.12/мес. (×0.86) → спрос 34 дн.: 1.08 + SLA 5% → запас 1.13 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -16324,12 +16324,12 @@
       </c>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BX</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BX] База 2.02/мес. (×0.74) → спрос 34 дн.: 1.68 + SLA 11% → запас 1.86 − ост. 1 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.02/мес. (×0.74) → спрос 34 дн.: 1.68 + SLA 11% → запас 1.86 − ост. 1 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -16381,12 +16381,12 @@
       </c>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 2.14/мес. (×1.13) → спрос 34 дн.: 2.69 + SLA 10% → запас 2.96 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 2.14/мес. (×1.13) → спрос 34 дн.: 2.69 + SLA 10% → запас 2.96 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -16438,12 +16438,12 @@
       </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.87/мес. (×0.80) → спрос 34 дн.: 0.79 + SLA 5% → запас 0.82 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.87/мес. (×0.80) → спрос 34 дн.: 0.79 + SLA 5% → запас 0.82 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -16495,12 +16495,12 @@
       </c>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M289" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 13.55/мес. (×1.09) → спрос 34 дн.: 16.51 + SLA 12% → запас 18.57 − ост. 8 = авто 11 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 13.55/мес. (×1.09) → спрос 34 дн.: 16.51 + SLA 12% → запас 18.57 − ост. 8 = авто 11 ед.</t>
         </is>
       </c>
     </row>
@@ -16552,12 +16552,12 @@
       </c>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M290" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 2.42/мес. (×0.58) → спрос 34 дн.: 1.56 + SLA 5% → запас 1.64 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.42/мес. (×0.58) → спрос 34 дн.: 1.56 + SLA 5% → запас 1.64 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -16609,12 +16609,12 @@
       </c>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M291" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 1.29/мес. (×2.62) → спрос 34 дн.: 3.77 + SLA 5% → запас 3.96 − ост. 0 = авто 4 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.29/мес. (×2.62) → спрос 34 дн.: 3.77 + SLA 5% → запас 3.96 − ост. 0 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -16666,12 +16666,12 @@
       </c>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M292" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 4.37/мес. (×1.69) → спрос 34 дн.: 8.26 + SLA 10% → запас 9.09 − ост. 0 = авто 9 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 4.37/мес. (×1.69) → спрос 34 дн.: 8.26 + SLA 10% → запас 9.09 − ост. 0 = авто 9 ед.</t>
         </is>
       </c>
     </row>
@@ -16723,12 +16723,12 @@
       </c>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M293" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 1.08/мес. (×1.07) (сглажено опт-выбросов: 1) → спрос 34 дн.: 1.29 + SLA 5% → запас 1.36 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.08/мес. (×1.07) (сглажено опт-выбросов: 1) → спрос 34 дн.: 1.29 + SLA 5% → запас 1.36 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -16780,12 +16780,12 @@
       </c>
       <c r="L294" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M294" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 3.30/мес. (×0.67) → спрос 34 дн.: 2.48 + SLA 5% → запас 2.60 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 3.30/мес. (×0.67) → спрос 34 дн.: 2.48 + SLA 5% → запас 2.60 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -16837,12 +16837,12 @@
       </c>
       <c r="L295" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M295" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 4.94/мес. (×0.64) → спрос 34 дн.: 3.54 + SLA 8% → запас 3.81 − ост. 0 = авто 4 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 4.94/мес. (×0.64) → спрос 34 дн.: 3.54 + SLA 8% → запас 3.81 − ост. 0 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -16894,12 +16894,12 @@
       </c>
       <c r="L296" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.84/мес. (×0.99) → спрос 34 дн.: 0.93 + SLA 5% → запас 0.98 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.84/мес. (×0.99) → спрос 34 дн.: 0.93 + SLA 5% → запас 0.98 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -16951,12 +16951,12 @@
       </c>
       <c r="L297" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M297" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.64/мес. (×1.23) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.88 + SLA 5% → запас 0.93 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.64/мес. (×1.23) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.88 + SLA 5% → запас 0.93 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -17008,12 +17008,12 @@
       </c>
       <c r="L298" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M298" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 4.03/мес. (×0.57) (сглажено опт-выбросов: 1) → спрос 34 дн.: 2.56 + SLA 5% → запас 2.69 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 4.03/мес. (×0.57) (сглажено опт-выбросов: 1) → спрос 34 дн.: 2.56 + SLA 5% → запас 2.69 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -17065,12 +17065,12 @@
       </c>
       <c r="L299" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M299" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.26/мес. (×0.37) → спрос 34 дн.: 0.52 + SLA 10% → запас 0.57 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.26/мес. (×0.37) → спрос 34 дн.: 0.52 + SLA 10% → запас 0.57 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -17122,12 +17122,12 @@
       </c>
       <c r="L300" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M300" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 4.64/мес. (×1.78) → спрос 34 дн.: 9.23 + SLA 8% → запас 9.96 − ост. 9 = авто 1 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 4.64/мес. (×1.78) → спрос 34 дн.: 9.23 + SLA 8% → запас 9.96 − ост. 9 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -17179,12 +17179,12 @@
       </c>
       <c r="L301" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 2.05/мес. (×1.34) (сглажено опт-выбросов: 1) → спрос 34 дн.: 3.06 + SLA 8% → запас 3.30 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.05/мес. (×1.34) (сглажено опт-выбросов: 1) → спрос 34 дн.: 3.06 + SLA 8% → запас 3.30 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -17236,12 +17236,12 @@
       </c>
       <c r="L302" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.64/мес. (×0.96) → спрос 34 дн.: 0.68 + SLA 8% → запас 0.74 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.64/мес. (×0.96) → спрос 34 дн.: 0.68 + SLA 8% → запас 0.74 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -17293,12 +17293,12 @@
       </c>
       <c r="L303" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 1.16/мес. (×0.64) → спрос 34 дн.: 0.83 + SLA 8% → запас 0.90 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.16/мес. (×0.64) → спрос 34 дн.: 0.83 + SLA 8% → запас 0.90 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -17350,12 +17350,12 @@
       </c>
       <c r="L304" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.64/мес. (×0.68) → спрос 34 дн.: 0.49 + SLA 8% → запас 0.53 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.64/мес. (×0.68) → спрос 34 дн.: 0.49 + SLA 8% → запас 0.53 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="L305" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 0.72/мес. (×1.07) → спрос 34 дн.: 0.86 + SLA 8% → запас 0.93 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.72/мес. (×1.07) → спрос 34 дн.: 0.86 + SLA 8% → запас 0.93 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -17464,12 +17464,12 @@
       </c>
       <c r="L306" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.43/мес. (×1.85) → спрос 34 дн.: 0.89 + SLA 5% → запас 0.93 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.43/мес. (×1.85) → спрос 34 дн.: 0.89 + SLA 5% → запас 0.93 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -17521,12 +17521,12 @@
       </c>
       <c r="L307" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M307" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.49/мес. (×1.02) → спрос 34 дн.: 0.55 + SLA 5% → запас 0.58 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.49/мес. (×1.02) → спрос 34 дн.: 0.55 + SLA 5% → запас 0.58 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -17578,12 +17578,12 @@
       </c>
       <c r="L308" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M308" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 0.63/мес. (×1.05) → спрос 34 дн.: 0.74 + SLA 8% → запас 0.80 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.63/мес. (×1.05) → спрос 34 дн.: 0.74 + SLA 8% → запас 0.80 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -17635,12 +17635,12 @@
       </c>
       <c r="L309" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M309" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 1.27/мес. (×0.38) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.54 + SLA 5% → запас 0.57 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 1.27/мес. (×0.38) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.54 + SLA 5% → запас 0.57 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -17692,12 +17692,12 @@
       </c>
       <c r="L310" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M310" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 1.84/мес. (×0.56) → спрос 34 дн.: 1.14 + SLA 8% → запас 1.24 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 1.84/мес. (×0.56) → спрос 34 дн.: 1.14 + SLA 8% → запас 1.24 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -17749,12 +17749,12 @@
       </c>
       <c r="L311" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M311" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 1.41/мес. (×0.43) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.67 + SLA 8% → запас 0.72 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 1.41/мес. (×0.43) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.67 + SLA 8% → запас 0.72 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -17806,12 +17806,12 @@
       </c>
       <c r="L312" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M312" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 4.43/мес. (×0.93) → спрос 34 дн.: 4.60 + SLA 8% → запас 4.95 − ост. 0 = авто 5 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 4.43/мес. (×0.93) → спрос 34 дн.: 4.60 + SLA 8% → запас 4.95 − ост. 0 = авто 5 ед.</t>
         </is>
       </c>
     </row>
@@ -17863,12 +17863,12 @@
       </c>
       <c r="L313" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M313" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 1.30/мес. (×1.76) → спрос 34 дн.: 2.55 + SLA 5% → запас 2.68 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 1.30/мес. (×1.76) → спрос 34 дн.: 2.55 + SLA 5% → запас 2.68 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -17920,12 +17920,12 @@
       </c>
       <c r="L314" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M314" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 11.20/мес. (×1.94) (сглажено опт-выбросов: 1) → спрос 34 дн.: 24.27 + SLA 12% → запас 27.06 − ост. 0 = авто 27 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 11.20/мес. (×1.94) (сглажено опт-выбросов: 1) → спрос 34 дн.: 24.27 + SLA 12% → запас 27.06 − ост. 0 = авто 27 ед.</t>
         </is>
       </c>
     </row>
@@ -17977,12 +17977,12 @@
       </c>
       <c r="L315" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M315" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 4.01/мес. (×0.43) → спрос 34 дн.: 1.92 + SLA 5% → запас 2.02 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 4.01/мес. (×0.43) → спрос 34 дн.: 1.92 + SLA 5% → запас 2.02 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -18034,12 +18034,12 @@
       </c>
       <c r="L316" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M316" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 9.01/мес. (×0.96) (сглажено опт-выбросов: 1) → спрос 34 дн.: 9.70 + SLA 12% → запас 10.91 − ост. 6 = авто 5 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 9.01/мес. (×0.96) (сглажено опт-выбросов: 1) → спрос 34 дн.: 9.70 + SLA 12% → запас 10.91 − ост. 6 = авто 5 ед.</t>
         </is>
       </c>
     </row>
@@ -18091,12 +18091,12 @@
       </c>
       <c r="L317" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M317" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 17.48/мес. (×0.59) → спрос 34 дн.: 11.46 + SLA 10% → запас 12.55 − ост. 0 = авто 13 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 17.48/мес. (×0.59) → спрос 34 дн.: 11.46 + SLA 10% → запас 12.55 − ост. 0 = авто 13 ед.</t>
         </is>
       </c>
     </row>
@@ -18148,12 +18148,12 @@
       </c>
       <c r="L318" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M318" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 7.75/мес. (×0.51) → спрос 34 дн.: 4.41 + SLA 12% → запас 4.92 − ост. 0 = авто 5 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 7.75/мес. (×0.51) → спрос 34 дн.: 4.41 + SLA 12% → запас 4.92 − ост. 0 = авто 5 ед.</t>
         </is>
       </c>
     </row>
@@ -18205,12 +18205,12 @@
       </c>
       <c r="L319" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M319" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 8.03/мес. (×0.38) → спрос 34 дн.: 3.41 + SLA 10% → запас 3.73 − ост. 0 = авто 4 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 8.03/мес. (×0.38) → спрос 34 дн.: 3.41 + SLA 10% → запас 3.73 − ост. 0 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -18262,12 +18262,12 @@
       </c>
       <c r="L320" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M320" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 8.39/мес. (×0.21) → спрос 34 дн.: 1.95 + SLA 12% → запас 2.18 − ост. 0 = авто 2 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 8.39/мес. (×0.21) → спрос 34 дн.: 1.95 + SLA 12% → запас 2.18 − ост. 0 = авто 2 ед.</t>
         </is>
       </c>
     </row>
@@ -18319,12 +18319,12 @@
       </c>
       <c r="L321" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M321" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 5.69/мес. (×0.75) → спрос 34 дн.: 4.80 + SLA 10% → запас 5.28 − ост. 0 = авто 5 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 5.69/мес. (×0.75) → спрос 34 дн.: 4.80 + SLA 10% → запас 5.28 − ост. 0 = авто 5 ед.</t>
         </is>
       </c>
     </row>
@@ -18376,12 +18376,12 @@
       </c>
       <c r="L322" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M322" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 6.23/мес. (×0.83) → спрос 34 дн.: 5.80 + SLA 8% → запас 6.26 − ост. 1 = авто 5 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 6.23/мес. (×0.83) → спрос 34 дн.: 5.80 + SLA 8% → запас 6.26 − ост. 1 = авто 5 ед.</t>
         </is>
       </c>
     </row>
@@ -18433,12 +18433,12 @@
       </c>
       <c r="L323" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M323" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 19.64/мес. (×0.66) → спрос 34 дн.: 14.48 + SLA 12% → запас 16.15 − ост. 0 = авто 16 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 19.64/мес. (×0.66) → спрос 34 дн.: 14.48 + SLA 12% → запас 16.15 − ост. 0 = авто 16 ед.</t>
         </is>
       </c>
     </row>
@@ -18490,12 +18490,12 @@
       </c>
       <c r="L324" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M324" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 19.76/мес. (×2.04) → спрос 34 дн.: 45.00 + SLA 12% → запас 50.17 − ост. 30 = авто 20 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 19.76/мес. (×2.04) → спрос 34 дн.: 45.00 + SLA 12% → запас 50.17 − ост. 30 = авто 20 ед.</t>
         </is>
       </c>
     </row>
@@ -18547,12 +18547,12 @@
       </c>
       <c r="L325" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M325" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 4.05/мес. (×2.48) → спрос 34 дн.: 11.19 + SLA 5% → запас 11.75 − ост. 0 = авто 12 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 4.05/мес. (×2.48) → спрос 34 дн.: 11.19 + SLA 5% → запас 11.75 − ост. 0 = авто 12 ед.</t>
         </is>
       </c>
     </row>
@@ -18604,12 +18604,12 @@
       </c>
       <c r="L326" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M326" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 14.47/мес. (×1.61) → спрос 34 дн.: 26.02 + SLA 10% → запас 28.62 − ост. 17 = авто 12 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 14.47/мес. (×1.61) → спрос 34 дн.: 26.02 + SLA 10% → запас 28.62 − ост. 17 = авто 12 ед.</t>
         </is>
       </c>
     </row>
@@ -18661,12 +18661,12 @@
       </c>
       <c r="L327" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M327" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 19.11/мес. (×0.68) → спрос 34 дн.: 14.49 + SLA 12% → запас 16.16 − ост. 0 = авто 16 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 19.11/мес. (×0.68) → спрос 34 дн.: 14.49 + SLA 12% → запас 16.16 − ост. 0 = авто 16 ед.</t>
         </is>
       </c>
     </row>
@@ -18718,12 +18718,12 @@
       </c>
       <c r="L328" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M328" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 16.90/мес. (×1.89) → спрос 34 дн.: 35.61 + SLA 12% → запас 39.71 − ост. 23 = авто 17 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 16.90/мес. (×1.89) → спрос 34 дн.: 35.61 + SLA 12% → запас 39.71 − ост. 23 = авто 17 ед.</t>
         </is>
       </c>
     </row>
@@ -18775,12 +18775,12 @@
       </c>
       <c r="L329" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M329" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 6.37/мес. (×0.62) (сглажено опт-выбросов: 1) → спрос 34 дн.: 4.45 + SLA 10% → запас 4.89 − ост. 0 = авто 5 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 6.37/мес. (×0.62) (сглажено опт-выбросов: 1) → спрос 34 дн.: 4.45 + SLA 10% → запас 4.89 − ост. 0 = авто 5 ед.</t>
         </is>
       </c>
     </row>
@@ -18832,12 +18832,12 @@
       </c>
       <c r="L330" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M330" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 15.89/мес. (×1.50) (сглажено опт-выбросов: 1) → спрос 34 дн.: 26.66 + SLA 12% → запас 29.73 − ост. 0 = авто 30 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 15.89/мес. (×1.50) (сглажено опт-выбросов: 1) → спрос 34 дн.: 26.66 + SLA 12% → запас 29.73 − ост. 0 = авто 30 ед.</t>
         </is>
       </c>
     </row>
@@ -18889,12 +18889,12 @@
       </c>
       <c r="L331" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M331" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CX] База 6.41/мес. (×0.89) → спрос 34 дн.: 6.40 + SLA 10% → запас 7.01 − ост. 0 = авто 7 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 6.41/мес. (×0.89) → спрос 34 дн.: 6.40 + SLA 10% → запас 7.01 − ост. 0 = авто 7 ед.</t>
         </is>
       </c>
     </row>
@@ -18946,12 +18946,12 @@
       </c>
       <c r="L332" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M332" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 14.73/мес. (×0.45) (сглажено опт-выбросов: 1) → спрос 34 дн.: 7.33 + SLA 8% → запас 7.92 − ост. 0 = авто 8 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 14.73/мес. (×0.45) (сглажено опт-выбросов: 1) → спрос 34 дн.: 7.33 + SLA 8% → запас 7.92 − ост. 0 = авто 8 ед.</t>
         </is>
       </c>
     </row>
@@ -19003,12 +19003,12 @@
       </c>
       <c r="L333" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BX</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M333" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BX] База 34.71/мес. (×0.56) → спрос 34 дн.: 21.75 + SLA 11% → запас 24.14 − ост. 0 = авто 24 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 34.71/мес. (×0.56) → спрос 34 дн.: 21.75 + SLA 11% → запас 24.14 − ост. 0 = авто 24 ед.</t>
         </is>
       </c>
     </row>
@@ -19060,12 +19060,12 @@
       </c>
       <c r="L334" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M334" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 12.39/мес. (×2.28) → спрос 34 дн.: 31.50 + SLA 10% → запас 34.65 − ост. 0 = авто 35 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 12.39/мес. (×2.28) → спрос 34 дн.: 31.50 + SLA 10% → запас 34.65 − ост. 0 = авто 35 ед.</t>
         </is>
       </c>
     </row>
@@ -19117,12 +19117,12 @@
       </c>
       <c r="L335" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M335" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 17.60/мес. (×1.74) → спрос 34 дн.: 34.17 + SLA 12% → запас 38.10 − ост. 0 = авто 38 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 17.60/мес. (×1.74) → спрос 34 дн.: 34.17 + SLA 12% → запас 38.10 − ост. 0 = авто 38 ед.</t>
         </is>
       </c>
     </row>
@@ -19174,12 +19174,12 @@
       </c>
       <c r="L336" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M336" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 13.98/мес. (×1.28) → спрос 34 дн.: 20.02 + SLA 10% → запас 21.92 − ост. 0 = авто 22 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 13.98/мес. (×1.28) → спрос 34 дн.: 20.02 + SLA 10% → запас 21.92 − ост. 0 = авто 22 ед.</t>
         </is>
       </c>
     </row>
@@ -19231,12 +19231,12 @@
       </c>
       <c r="L337" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M337" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 17.03/мес. (×1.38) → спрос 34 дн.: 26.30 + SLA 10% → запас 28.80 − ост. 0 = авто 29 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 17.03/мес. (×1.38) → спрос 34 дн.: 26.30 + SLA 10% → запас 28.80 − ост. 0 = авто 29 ед.</t>
         </is>
       </c>
     </row>
@@ -19288,12 +19288,12 @@
       </c>
       <c r="L338" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M338" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.76/мес. (×0.68) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.58 + SLA 5% → запас 0.61 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.76/мес. (×0.68) (сглажено опт-выбросов: 1) → спрос 34 дн.: 0.58 + SLA 5% → запас 0.61 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -19345,12 +19345,12 @@
       </c>
       <c r="L339" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M339" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 8.48/мес. (×0.62) → спрос 34 дн.: 5.86 + SLA 10% → запас 6.42 − ост. 0 = авто 6 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 8.48/мес. (×0.62) → спрос 34 дн.: 5.86 + SLA 10% → запас 6.42 − ост. 0 = авто 6 ед.</t>
         </is>
       </c>
     </row>
@@ -19402,12 +19402,12 @@
       </c>
       <c r="L340" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M340" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 15.29/мес. (×0.52) → спрос 34 дн.: 8.83 + SLA 10% → запас 9.71 − ост. 0 = авто 10 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 15.29/мес. (×0.52) → спрос 34 дн.: 8.83 + SLA 10% → запас 9.71 − ост. 0 = авто 10 ед.</t>
         </is>
       </c>
     </row>
@@ -19459,12 +19459,12 @@
       </c>
       <c r="L341" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZ</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M341" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AZ] База 19.18/мес. (×1.16) → спрос 34 дн.: 24.89 + SLA 10% → запас 27.25 − ост. 5 = авто 22 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 19.18/мес. (×1.16) → спрос 34 дн.: 24.89 + SLA 10% → запас 27.25 − ост. 5 = авто 22 ед.</t>
         </is>
       </c>
     </row>
@@ -19516,12 +19516,12 @@
       </c>
       <c r="L342" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M342" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 17.47/мес. (×0.76) → спрос 34 дн.: 14.84 + SLA 12% → запас 16.54 − ост. 0 = авто 17 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 17.47/мес. (×0.76) → спрос 34 дн.: 14.84 + SLA 12% → запас 16.54 − ост. 0 = авто 17 ед.</t>
         </is>
       </c>
     </row>
@@ -19573,12 +19573,12 @@
       </c>
       <c r="L343" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M343" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 2.31/мес. (×1.19) → спрос 34 дн.: 3.08 + SLA 5% → запас 3.23 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 2.31/мес. (×1.19) → спрос 34 дн.: 3.08 + SLA 5% → запас 3.23 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -19630,12 +19630,12 @@
       </c>
       <c r="L344" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M344" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CY] База 11.75/мес. (×1.74) → спрос 34 дн.: 22.87 + SLA 8% → запас 24.70 − ост. 0 = авто 25 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 11.75/мес. (×1.74) → спрос 34 дн.: 22.87 + SLA 8% → запас 24.70 − ост. 0 = авто 25 ед.</t>
         </is>
       </c>
     </row>
@@ -19687,12 +19687,12 @@
       </c>
       <c r="L345" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M345" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 3.61/мес. (×0.75) → спрос 34 дн.: 3.03 + SLA 5% → запас 3.18 − ост. 0 = авто 3 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 3.61/мес. (×0.75) → спрос 34 дн.: 3.03 + SLA 5% → запас 3.18 − ост. 0 = авто 3 ед.</t>
         </is>
       </c>
     </row>
@@ -19744,12 +19744,12 @@
       </c>
       <c r="L346" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M346" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 9.83/мес. (×0.37) → спрос 34 дн.: 4.04 + SLA 10% → запас 4.45 − ост. 0 = авто 4 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 9.83/мес. (×0.37) → спрос 34 дн.: 4.04 + SLA 10% → запас 4.45 − ост. 0 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -19801,12 +19801,12 @@
       </c>
       <c r="L347" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M347" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 17.57/мес. (×0.58) → спрос 34 дн.: 11.32 + SLA 12% → запас 12.62 − ост. 5 = авто 8 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 17.57/мес. (×0.58) → спрос 34 дн.: 11.32 + SLA 12% → запас 12.62 − ост. 5 = авто 8 ед.</t>
         </is>
       </c>
     </row>
@@ -19858,12 +19858,12 @@
       </c>
       <c r="L348" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">5-Высокий</t>
         </is>
       </c>
       <c r="M348" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 27.44/мес. (×0.48) → спрос 34 дн.: 14.83 + SLA 12% → запас 16.53 − ост. 2 = авто 15 ед.</t>
+          <t xml:space="preserve">[5-Высокий] База 27.44/мес. (×0.48) → спрос 34 дн.: 14.83 + SLA 12% → запас 16.53 − ост. 2 = авто 15 ед.</t>
         </is>
       </c>
     </row>
@@ -19915,12 +19915,12 @@
       </c>
       <c r="L349" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">3-Средний</t>
         </is>
       </c>
       <c r="M349" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 3.50/мес. (×0.84) → спрос 34 дн.: 3.30 + SLA 5% → запас 3.47 − ост. 2 = авто 1 ед.</t>
+          <t xml:space="preserve">[3-Средний] База 3.50/мес. (×0.84) → спрос 34 дн.: 3.30 + SLA 5% → запас 3.47 − ост. 2 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -19972,12 +19972,12 @@
       </c>
       <c r="L350" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M350" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.52/мес. (×1.29) → спрос 34 дн.: 0.76 + SLA 5% → запас 0.80 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.52/мес. (×1.29) → спрос 34 дн.: 0.76 + SLA 5% → запас 0.80 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -20029,12 +20029,12 @@
       </c>
       <c r="L351" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M351" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 2.20/мес. (×1.34) → спрос 34 дн.: 3.29 + SLA 12% → запас 3.67 − ост. 0 = авто 4 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 2.20/мес. (×1.34) → спрос 34 дн.: 3.29 + SLA 12% → запас 3.67 − ост. 0 = авто 4 ед.</t>
         </is>
       </c>
     </row>
@@ -20086,12 +20086,12 @@
       </c>
       <c r="L352" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M352" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CZ] База 0.38/мес. (×1.71) → спрос 34 дн.: 0.72 + SLA 5% → запас 0.76 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.38/мес. (×1.71) → спрос 34 дн.: 0.72 + SLA 5% → запас 0.76 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -20143,12 +20143,12 @@
       </c>
       <c r="L353" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M353" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AY] База 0.66/мес. (×0.79) → спрос 34 дн.: 0.58 + SLA 12% → запас 0.65 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.66/мес. (×0.79) → спрос 34 дн.: 0.58 + SLA 12% → запас 0.65 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -20200,12 +20200,12 @@
       </c>
       <c r="L354" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">1-Низкий</t>
         </is>
       </c>
       <c r="M354" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.70/мес. (×0.84) → спрос 34 дн.: 0.65 + SLA 10% → запас 0.72 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[1-Низкий] База 0.70/мес. (×0.84) → спрос 34 дн.: 0.65 + SLA 10% → запас 0.72 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -20257,12 +20257,12 @@
       </c>
       <c r="L355" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AX</t>
+          <t xml:space="preserve">4-Выше среднего</t>
         </is>
       </c>
       <c r="M355" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[AX] База 3.26/мес. (×1.45) (сглажено опт-выбросов: 1) → спрос 34 дн.: 5.28 + SLA 12% → запас 5.94 − ост. 0 = авто 6 ед.</t>
+          <t xml:space="preserve">[4-Выше среднего] База 3.26/мес. (×1.45) (сглажено опт-выбросов: 1) → спрос 34 дн.: 5.28 + SLA 12% → запас 5.94 − ост. 0 = авто 6 ед.</t>
         </is>
       </c>
     </row>
@@ -20314,12 +20314,12 @@
       </c>
       <c r="L356" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M356" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.34/мес. (×0.80) → спрос 34 дн.: 1.21 + SLA 10% → запас 1.33 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 1.34/мес. (×0.80) → спрос 34 дн.: 1.21 + SLA 10% → запас 1.33 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -20371,12 +20371,12 @@
       </c>
       <c r="L357" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M357" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 0.28/мес. (×2.24) → спрос 34 дн.: 0.69 + SLA 8% → запас 0.74 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.28/мес. (×2.24) → спрос 34 дн.: 0.69 + SLA 8% → запас 0.74 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -20428,12 +20428,12 @@
       </c>
       <c r="L358" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M358" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 0.90/мес. (×0.80) → спрос 34 дн.: 0.81 + SLA 10% → запас 0.89 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 0.90/мес. (×0.80) → спрос 34 дн.: 0.81 + SLA 10% → запас 0.89 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -20485,12 +20485,12 @@
       </c>
       <c r="L359" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY</t>
+          <t xml:space="preserve">2-Ниже среднего</t>
         </is>
       </c>
       <c r="M359" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BY] База 1.38/мес. (×0.80) → спрос 34 дн.: 1.24 + SLA 10% → запас 1.36 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[2-Ниже среднего] База 1.38/мес. (×0.80) → спрос 34 дн.: 1.24 + SLA 10% → запас 1.36 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -20542,12 +20542,12 @@
       </c>
       <c r="L360" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M360" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 0.21/мес. (×2.05) → спрос 34 дн.: 0.47 + SLA 8% → запас 0.51 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.21/мес. (×2.05) → спрос 34 дн.: 0.47 + SLA 8% → запас 0.51 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -20599,12 +20599,12 @@
       </c>
       <c r="L361" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M361" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 0.25/мес. (×1.88) → спрос 34 дн.: 0.53 + SLA 8% → запас 0.57 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.25/мес. (×1.88) → спрос 34 дн.: 0.53 + SLA 8% → запас 0.57 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>
@@ -20656,12 +20656,12 @@
       </c>
       <c r="L362" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ</t>
+          <t xml:space="preserve">0-Нет продаж</t>
         </is>
       </c>
       <c r="M362" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[BZ] База 0.34/мес. (×2.40) → спрос 34 дн.: 0.92 + SLA 8% → запас 0.99 − ост. 0 = авто 1 ед.</t>
+          <t xml:space="preserve">[0-Нет продаж] База 0.34/мес. (×2.40) → спрос 34 дн.: 0.92 + SLA 8% → запас 0.99 − ост. 0 = авто 1 ед.</t>
         </is>
       </c>
     </row>

--- a/Заявки поставщикам (авторасчёт).xlsx
+++ b/Заявки поставщикам (авторасчёт).xlsx
@@ -20686,38 +20686,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Склад</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Поставщик</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Всего SKU</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">SKU к закупке</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Единиц к закупке</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Сумма закупки (руб.)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Доля бюджета (%)</t>
         </is>
@@ -20726,748 +20732,972 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ООО "ГолдДекор"</t>
         </is>
       </c>
-      <c r="B2" s="6">
+      <c r="C2" s="6">
         <v>260</v>
       </c>
-      <c r="C2" s="6">
+      <c r="D2" s="6">
         <v>86</v>
       </c>
-      <c r="D2" s="3">
+      <c r="E2" s="3">
         <v>215</v>
       </c>
-      <c r="E2" s="4">
+      <c r="F2" s="4">
         <v>2230.49</v>
       </c>
-      <c r="F2" s="4">
+      <c r="G2" s="4">
         <v>39.1</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ООО "Оберег Торг"</t>
         </is>
       </c>
-      <c r="B3" s="6">
+      <c r="C3" s="6">
         <v>913</v>
       </c>
-      <c r="C3" s="6">
+      <c r="D3" s="6">
         <v>168</v>
       </c>
-      <c r="D3" s="3">
+      <c r="E3" s="3">
         <v>762</v>
       </c>
-      <c r="E3" s="4">
+      <c r="F3" s="4">
         <v>1684.79</v>
       </c>
-      <c r="F3" s="4">
+      <c r="G3" s="4">
         <v>29.54</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ООО "Цветогамма"</t>
         </is>
       </c>
-      <c r="B4" s="6">
+      <c r="C4" s="6">
         <v>82</v>
       </c>
-      <c r="C4" s="6">
+      <c r="D4" s="6">
         <v>16</v>
       </c>
-      <c r="D4" s="3">
+      <c r="E4" s="3">
         <v>19</v>
       </c>
-      <c r="E4" s="4">
+      <c r="F4" s="4">
         <v>386.36</v>
       </c>
-      <c r="F4" s="4">
+      <c r="G4" s="4">
         <v>6.77</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ООО "ДЖИ ДИСТРИБЬЮШН"</t>
         </is>
       </c>
-      <c r="B5" s="6">
+      <c r="C5" s="6">
         <v>45</v>
       </c>
-      <c r="C5" s="6">
+      <c r="D5" s="6">
         <v>22</v>
       </c>
-      <c r="D5" s="3">
+      <c r="E5" s="3">
         <v>33</v>
       </c>
-      <c r="E5" s="4">
+      <c r="F5" s="4">
         <v>357.92</v>
       </c>
-      <c r="F5" s="4">
+      <c r="G5" s="4">
         <v>6.27</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ООО "СИСТЕМА ООО"</t>
         </is>
       </c>
-      <c r="B6" s="6">
-        <v>49</v>
-      </c>
       <c r="C6" s="6">
-        <v>8</v>
-      </c>
-      <c r="D6" s="3">
-        <v>23</v>
-      </c>
-      <c r="E6" s="4">
-        <v>289.23</v>
+        <v>48</v>
+      </c>
+      <c r="D6" s="6">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3">
+        <v>19</v>
       </c>
       <c r="F6" s="4">
-        <v>5.07</v>
+        <v>272.27</v>
+      </c>
+      <c r="G6" s="4">
+        <v>4.77</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ЧУП "МАВ"</t>
         </is>
       </c>
-      <c r="B7" s="6">
+      <c r="C7" s="6">
         <v>119</v>
       </c>
-      <c r="C7" s="6">
+      <c r="D7" s="6">
         <v>9</v>
       </c>
-      <c r="D7" s="3">
+      <c r="E7" s="3">
         <v>9</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <v>211.36</v>
       </c>
-      <c r="F7" s="4">
+      <c r="G7" s="4">
         <v>3.71</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ООО "ТД Комплект"</t>
         </is>
       </c>
-      <c r="B8" s="6">
-        <v>139</v>
-      </c>
       <c r="C8" s="6">
-        <v>17</v>
-      </c>
-      <c r="D8" s="3">
-        <v>61</v>
-      </c>
-      <c r="E8" s="4">
-        <v>201.64</v>
+        <v>81</v>
+      </c>
+      <c r="D8" s="6">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3">
+        <v>50</v>
       </c>
       <c r="F8" s="4">
-        <v>3.53</v>
+        <v>114.63</v>
+      </c>
+      <c r="G8" s="4">
+        <v>2.01</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">ЧТУП "АвтоНикахим"</t>
         </is>
       </c>
-      <c r="B9" s="6">
+      <c r="C9" s="6">
         <v>19</v>
       </c>
-      <c r="C9" s="6">
+      <c r="D9" s="6">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="E9" s="3">
         <v>14</v>
       </c>
-      <c r="E9" s="4">
+      <c r="F9" s="4">
         <v>106.3</v>
       </c>
-      <c r="F9" s="4">
+      <c r="G9" s="4">
         <v>1.86</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО "ПилотЭлектроПлюс"</t>
-        </is>
-      </c>
-      <c r="B10" s="6">
-        <v>15</v>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "ТД Комплект"</t>
+        </is>
       </c>
       <c r="C10" s="6">
-        <v>5</v>
-      </c>
-      <c r="D10" s="3">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4">
-        <v>79.6</v>
+        <v>58</v>
+      </c>
+      <c r="D10" s="6">
+        <v>7</v>
+      </c>
+      <c r="E10" s="3">
+        <v>11</v>
       </c>
       <c r="F10" s="4">
-        <v>1.4</v>
+        <v>87.01</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1.53</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО"Ома"</t>
-        </is>
-      </c>
-      <c r="B11" s="6">
-        <v>26</v>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "ПилотЭлектроПлюс"</t>
+        </is>
       </c>
       <c r="C11" s="6">
+        <v>15</v>
+      </c>
+      <c r="D11" s="6">
         <v>5</v>
       </c>
-      <c r="D11" s="3">
-        <v>7</v>
-      </c>
-      <c r="E11" s="4">
-        <v>55.75</v>
+      <c r="E11" s="3">
+        <v>9</v>
       </c>
       <c r="F11" s="4">
-        <v>0.98</v>
+        <v>79.6</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1.4</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО "Неманэлектрострой"</t>
-        </is>
-      </c>
-      <c r="B12" s="6">
-        <v>10</v>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО"Ома"</t>
+        </is>
       </c>
       <c r="C12" s="6">
-        <v>4</v>
-      </c>
-      <c r="D12" s="3">
-        <v>8</v>
-      </c>
-      <c r="E12" s="4">
-        <v>40.85</v>
+        <v>26</v>
+      </c>
+      <c r="D12" s="6">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>7</v>
       </c>
       <c r="F12" s="4">
-        <v>0.72</v>
+        <v>55.75</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0.98</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СООО "АСБ Фарбен-Бел"</t>
-        </is>
-      </c>
-      <c r="B13" s="6">
-        <v>42</v>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "Неманэлектрострой"</t>
+        </is>
       </c>
       <c r="C13" s="6">
-        <v>5</v>
-      </c>
-      <c r="D13" s="3">
-        <v>5</v>
-      </c>
-      <c r="E13" s="4">
-        <v>31.85</v>
+        <v>10</v>
+      </c>
+      <c r="D13" s="6">
+        <v>4</v>
+      </c>
+      <c r="E13" s="3">
+        <v>8</v>
       </c>
       <c r="F13" s="4">
-        <v>0.56</v>
+        <v>40.85</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0.72</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОДО "Роспродукт"</t>
-        </is>
-      </c>
-      <c r="B14" s="6">
-        <v>26</v>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СООО "АСБ Фарбен-Бел"</t>
+        </is>
       </c>
       <c r="C14" s="6">
-        <v>6</v>
-      </c>
-      <c r="D14" s="3">
-        <v>7</v>
-      </c>
-      <c r="E14" s="4">
-        <v>16.33</v>
+        <v>42</v>
+      </c>
+      <c r="D14" s="6">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5</v>
       </c>
       <c r="F14" s="4">
-        <v>0.29</v>
+        <v>31.85</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0.56</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО "Ю-ПЛАСТ-Бел"</t>
-        </is>
-      </c>
-      <c r="B15" s="6">
-        <v>1</v>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "СИСТЕМА ООО"</t>
+        </is>
       </c>
       <c r="C15" s="6">
         <v>1</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="6">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
         <v>4</v>
       </c>
-      <c r="E15" s="4">
-        <v>6.88</v>
-      </c>
       <c r="F15" s="4">
-        <v>0.12</v>
+        <v>16.96</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.3</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО "Магнум маркет плюс"</t>
-        </is>
-      </c>
-      <c r="B16" s="6">
-        <v>3</v>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ОДО "Роспродукт"</t>
+        </is>
       </c>
       <c r="C16" s="6">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4">
-        <v>2.48</v>
+        <v>26</v>
+      </c>
+      <c r="D16" s="6">
+        <v>6</v>
+      </c>
+      <c r="E16" s="3">
+        <v>7</v>
       </c>
       <c r="F16" s="4">
-        <v>0.04</v>
+        <v>16.33</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.29</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО "БелАдмиралСтрой"</t>
-        </is>
-      </c>
-      <c r="B17" s="6">
-        <v>3</v>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "Ю-ПЛАСТ-Бел"</t>
+        </is>
       </c>
       <c r="C17" s="6">
         <v>1</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="6">
         <v>1</v>
       </c>
-      <c r="E17" s="4">
-        <v>2.35</v>
+      <c r="E17" s="3">
+        <v>4</v>
       </c>
       <c r="F17" s="4">
-        <v>0.04</v>
+        <v>6.88</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0.12</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Поставщик не указан)</t>
-        </is>
-      </c>
-      <c r="B18" s="6">
-        <v>5</v>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "Магнум маркет плюс"</t>
+        </is>
       </c>
       <c r="C18" s="6">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1</v>
       </c>
       <c r="F18" s="4">
-        <v>0</v>
+        <v>2.48</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0.04</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОАО "Белхозторг"</t>
-        </is>
-      </c>
-      <c r="B19" s="6">
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "БелАдмиралСтрой"</t>
+        </is>
+      </c>
+      <c r="C19" s="6">
+        <v>3</v>
+      </c>
+      <c r="D19" s="6">
         <v>1</v>
       </c>
-      <c r="C19" s="6">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3">
-        <v>0</v>
-      </c>
-      <c r="E19" s="4">
-        <v>0</v>
+      <c r="E19" s="3">
+        <v>1</v>
       </c>
       <c r="F19" s="4">
-        <v>0</v>
+        <v>2.35</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0.04</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОАО "Лакокраска"</t>
-        </is>
-      </c>
-      <c r="B20" s="6">
-        <v>7</v>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(Поставщик не указан)</t>
+        </is>
       </c>
       <c r="C20" s="6">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="4">
+        <v>5</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="4">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОАО "Новогрудский завод металлоизделий"</t>
-        </is>
-      </c>
-      <c r="B21" s="6">
-        <v>1</v>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ОАО "Лакокраска"</t>
+        </is>
       </c>
       <c r="C21" s="6">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3">
-        <v>0</v>
-      </c>
-      <c r="E21" s="4">
+        <v>7</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>0</v>
       </c>
       <c r="F21" s="4">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОДО "Белоптторг"</t>
-        </is>
-      </c>
-      <c r="B22" s="6">
-        <v>5</v>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "Культбытхозторгплюс"</t>
+        </is>
       </c>
       <c r="C22" s="6">
-        <v>0</v>
-      </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="4">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО "ВергоХоз"</t>
-        </is>
-      </c>
-      <c r="B23" s="6">
-        <v>13</v>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "ПрофиФарб"</t>
+        </is>
       </c>
       <c r="C23" s="6">
-        <v>0</v>
-      </c>
-      <c r="D23" s="3">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4">
+        <v>3</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>0</v>
       </c>
       <c r="F23" s="4">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО "Культбытхозторгплюс"</t>
-        </is>
-      </c>
-      <c r="B24" s="6">
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "Сплендор"</t>
+        </is>
+      </c>
+      <c r="C24" s="6">
         <v>1</v>
       </c>
-      <c r="C24" s="6">
-        <v>0</v>
-      </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="4">
+      <c r="D24" s="6">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>0</v>
       </c>
       <c r="F24" s="4">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО "ПрофиФарб"</t>
-        </is>
-      </c>
-      <c r="B25" s="6">
-        <v>3</v>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "Стройбазторг"</t>
+        </is>
       </c>
       <c r="C25" s="6">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3">
-        <v>0</v>
-      </c>
-      <c r="E25" s="4">
+        <v>7</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
         <v>0</v>
       </c>
       <c r="F25" s="4">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО "Скобяной трейд"</t>
-        </is>
-      </c>
-      <c r="B26" s="6">
-        <v>5</v>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "ФабрикаКрасок"</t>
+        </is>
       </c>
       <c r="C26" s="6">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3">
-        <v>0</v>
-      </c>
-      <c r="E26" s="4">
+        <v>11</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>0</v>
       </c>
       <c r="F26" s="4">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО "Сплендор"</t>
-        </is>
-      </c>
-      <c r="B27" s="6">
-        <v>1</v>
+          <t xml:space="preserve">Склад Кореличи</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">УП"Каприз"</t>
+        </is>
       </c>
       <c r="C27" s="6">
-        <v>0</v>
-      </c>
-      <c r="D27" s="3">
-        <v>0</v>
-      </c>
-      <c r="E27" s="4">
+        <v>23</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>0</v>
       </c>
       <c r="F27" s="4">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО "Стройбазторг"</t>
-        </is>
-      </c>
-      <c r="B28" s="6">
-        <v>7</v>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ОАО "Белхозторг"</t>
+        </is>
       </c>
       <c r="C28" s="6">
-        <v>0</v>
-      </c>
-      <c r="D28" s="3">
-        <v>0</v>
-      </c>
-      <c r="E28" s="4">
+        <v>1</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
         <v>0</v>
       </c>
       <c r="F28" s="4">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО "ФабрикаКрасок"</t>
-        </is>
-      </c>
-      <c r="B29" s="6">
-        <v>11</v>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ОАО "Новогрудский завод металлоизделий"</t>
+        </is>
       </c>
       <c r="C29" s="6">
-        <v>0</v>
-      </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4">
+        <v>1</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>0</v>
       </c>
       <c r="F29" s="4">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО "Южный Океан"</t>
-        </is>
-      </c>
-      <c r="B30" s="6">
-        <v>1</v>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ОДО "Белоптторг"</t>
+        </is>
       </c>
       <c r="C30" s="6">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3">
-        <v>0</v>
-      </c>
-      <c r="E30" s="4">
+        <v>5</v>
+      </c>
+      <c r="D30" s="6">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3">
         <v>0</v>
       </c>
       <c r="F30" s="4">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООО"Грифон Голд"</t>
-        </is>
-      </c>
-      <c r="B31" s="6">
-        <v>9</v>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "ВергоХоз"</t>
+        </is>
       </c>
       <c r="C31" s="6">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3">
-        <v>0</v>
-      </c>
-      <c r="E31" s="4">
+        <v>13</v>
+      </c>
+      <c r="D31" s="6">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3">
         <v>0</v>
       </c>
       <c r="F31" s="4">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СООО "ПП Полесье"</t>
-        </is>
-      </c>
-      <c r="B32" s="6">
-        <v>3</v>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "Скобяной трейд"</t>
+        </is>
       </c>
       <c r="C32" s="6">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="4">
+        <v>5</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="4">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">СП "Дельфа-Буг"</t>
-        </is>
-      </c>
-      <c r="B33" s="6">
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО "Южный Океан"</t>
+        </is>
+      </c>
+      <c r="C33" s="6">
         <v>1</v>
       </c>
-      <c r="C33" s="6">
-        <v>0</v>
-      </c>
-      <c r="D33" s="3">
-        <v>0</v>
-      </c>
-      <c r="E33" s="4">
+      <c r="D33" s="6">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>0</v>
       </c>
       <c r="F33" s="4">
+        <v>0</v>
+      </c>
+      <c r="G33" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">УП "Бакалея"</t>
-        </is>
-      </c>
-      <c r="B34" s="6">
-        <v>1</v>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ООО"Грифон Голд"</t>
+        </is>
       </c>
       <c r="C34" s="6">
-        <v>0</v>
-      </c>
-      <c r="D34" s="3">
-        <v>0</v>
-      </c>
-      <c r="E34" s="4">
+        <v>9</v>
+      </c>
+      <c r="D34" s="6">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3">
         <v>0</v>
       </c>
       <c r="F34" s="4">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">УП"Каприз"</t>
-        </is>
-      </c>
-      <c r="B35" s="6">
-        <v>23</v>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СООО "ПП Полесье"</t>
+        </is>
       </c>
       <c r="C35" s="6">
-        <v>0</v>
-      </c>
-      <c r="D35" s="3">
-        <v>0</v>
-      </c>
-      <c r="E35" s="4">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>0</v>
       </c>
       <c r="F35" s="4">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">СП "Дельфа-Буг"</t>
+        </is>
+      </c>
+      <c r="C36" s="6">
+        <v>1</v>
+      </c>
+      <c r="D36" s="6">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Склад Мир</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">УП "Бакалея"</t>
+        </is>
+      </c>
+      <c r="C37" s="6">
+        <v>1</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4">
         <v>0</v>
       </c>
     </row>
@@ -21682,12 +21912,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Продажи 12м</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Остаток</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Продажи 12м</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -21731,10 +21961,10 @@
         </is>
       </c>
       <c r="G2" s="6">
+        <v>14</v>
+      </c>
+      <c r="H2" s="6">
         <v>22</v>
-      </c>
-      <c r="H2" s="6">
-        <v>14</v>
       </c>
       <c r="I2" s="4">
         <v>900</v>
@@ -21773,10 +22003,10 @@
         </is>
       </c>
       <c r="G3" s="6">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6">
         <v>6</v>
-      </c>
-      <c r="H3" s="6">
-        <v>1</v>
       </c>
       <c r="I3" s="4">
         <v>861.3</v>
@@ -21815,10 +22045,10 @@
         </is>
       </c>
       <c r="G4" s="6">
+        <v>3</v>
+      </c>
+      <c r="H4" s="6">
         <v>11</v>
-      </c>
-      <c r="H4" s="6">
-        <v>3</v>
       </c>
       <c r="I4" s="4">
         <v>799.2</v>
@@ -21857,10 +22087,10 @@
         </is>
       </c>
       <c r="G5" s="6">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6">
         <v>6</v>
-      </c>
-      <c r="H5" s="6">
-        <v>0</v>
       </c>
       <c r="I5" s="4">
         <v>804.2</v>
@@ -21899,10 +22129,10 @@
         </is>
       </c>
       <c r="G6" s="6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
         <v>5</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0</v>
       </c>
       <c r="I6" s="4">
         <v>999</v>
@@ -21941,10 +22171,10 @@
         </is>
       </c>
       <c r="G7" s="6">
+        <v>2</v>
+      </c>
+      <c r="H7" s="6">
         <v>4</v>
-      </c>
-      <c r="H7" s="6">
-        <v>2</v>
       </c>
       <c r="I7" s="4">
         <v>999</v>
@@ -21983,10 +22213,10 @@
         </is>
       </c>
       <c r="G8" s="6">
+        <v>15</v>
+      </c>
+      <c r="H8" s="6">
         <v>60</v>
-      </c>
-      <c r="H8" s="6">
-        <v>15</v>
       </c>
       <c r="I8" s="4">
         <v>730.7</v>
@@ -22025,10 +22255,10 @@
         </is>
       </c>
       <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
         <v>12</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0</v>
       </c>
       <c r="I9" s="4">
         <v>999</v>
@@ -22067,10 +22297,10 @@
         </is>
       </c>
       <c r="G10" s="6">
+        <v>5</v>
+      </c>
+      <c r="H10" s="6">
         <v>9</v>
-      </c>
-      <c r="H10" s="6">
-        <v>5</v>
       </c>
       <c r="I10" s="4">
         <v>999</v>
@@ -22109,10 +22339,10 @@
         </is>
       </c>
       <c r="G11" s="6">
+        <v>11</v>
+      </c>
+      <c r="H11" s="6">
         <v>9</v>
-      </c>
-      <c r="H11" s="6">
-        <v>11</v>
       </c>
       <c r="I11" s="4">
         <v>390.7</v>
@@ -22151,10 +22381,10 @@
         </is>
       </c>
       <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
         <v>6</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0</v>
       </c>
       <c r="I12" s="4">
         <v>999</v>
@@ -22193,10 +22423,10 @@
         </is>
       </c>
       <c r="G13" s="6">
+        <v>10</v>
+      </c>
+      <c r="H13" s="6">
         <v>14</v>
-      </c>
-      <c r="H13" s="6">
-        <v>10</v>
       </c>
       <c r="I13" s="4">
         <v>516.5</v>
@@ -22235,10 +22465,10 @@
         </is>
       </c>
       <c r="G14" s="6">
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
         <v>5</v>
-      </c>
-      <c r="H14" s="6">
-        <v>1</v>
       </c>
       <c r="I14" s="4">
         <v>999</v>
@@ -22277,10 +22507,10 @@
         </is>
       </c>
       <c r="G15" s="6">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6">
         <v>10</v>
-      </c>
-      <c r="H15" s="6">
-        <v>0</v>
       </c>
       <c r="I15" s="4">
         <v>999</v>
@@ -22319,10 +22549,10 @@
         </is>
       </c>
       <c r="G16" s="6">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
         <v>10</v>
-      </c>
-      <c r="H16" s="6">
-        <v>0</v>
       </c>
       <c r="I16" s="4">
         <v>999</v>
@@ -22361,10 +22591,10 @@
         </is>
       </c>
       <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
         <v>10</v>
-      </c>
-      <c r="H17" s="6">
-        <v>0</v>
       </c>
       <c r="I17" s="4">
         <v>999</v>
@@ -22403,10 +22633,10 @@
         </is>
       </c>
       <c r="G18" s="6">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6">
         <v>5</v>
-      </c>
-      <c r="H18" s="6">
-        <v>0</v>
       </c>
       <c r="I18" s="4">
         <v>999</v>
@@ -22445,10 +22675,10 @@
         </is>
       </c>
       <c r="G19" s="6">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6">
         <v>5</v>
-      </c>
-      <c r="H19" s="6">
-        <v>0</v>
       </c>
       <c r="I19" s="4">
         <v>999</v>
@@ -22487,10 +22717,10 @@
         </is>
       </c>
       <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
         <v>5</v>
-      </c>
-      <c r="H20" s="6">
-        <v>0</v>
       </c>
       <c r="I20" s="4">
         <v>999</v>
@@ -22529,10 +22759,10 @@
         </is>
       </c>
       <c r="G21" s="6">
+        <v>1</v>
+      </c>
+      <c r="H21" s="6">
         <v>9</v>
-      </c>
-      <c r="H21" s="6">
-        <v>1</v>
       </c>
       <c r="I21" s="4">
         <v>942.7</v>
@@ -22571,10 +22801,10 @@
         </is>
       </c>
       <c r="G22" s="6">
+        <v>38</v>
+      </c>
+      <c r="H22" s="6">
         <v>42</v>
-      </c>
-      <c r="H22" s="6">
-        <v>38</v>
       </c>
       <c r="I22" s="4">
         <v>651.2</v>
@@ -22613,10 +22843,10 @@
         </is>
       </c>
       <c r="G23" s="6">
+        <v>4</v>
+      </c>
+      <c r="H23" s="6">
         <v>15</v>
-      </c>
-      <c r="H23" s="6">
-        <v>4</v>
       </c>
       <c r="I23" s="4">
         <v>999</v>
@@ -22655,10 +22885,10 @@
         </is>
       </c>
       <c r="G24" s="6">
+        <v>1</v>
+      </c>
+      <c r="H24" s="6">
         <v>4</v>
-      </c>
-      <c r="H24" s="6">
-        <v>1</v>
       </c>
       <c r="I24" s="4">
         <v>963.9</v>
@@ -22697,10 +22927,10 @@
         </is>
       </c>
       <c r="G25" s="6">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6">
         <v>11</v>
-      </c>
-      <c r="H25" s="6">
-        <v>0</v>
       </c>
       <c r="I25" s="4">
         <v>999</v>
@@ -22739,10 +22969,10 @@
         </is>
       </c>
       <c r="G26" s="6">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6">
         <v>7</v>
-      </c>
-      <c r="H26" s="6">
-        <v>0</v>
       </c>
       <c r="I26" s="4">
         <v>999</v>
@@ -22781,10 +23011,10 @@
         </is>
       </c>
       <c r="G27" s="6">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6">
         <v>5</v>
-      </c>
-      <c r="H27" s="6">
-        <v>0</v>
       </c>
       <c r="I27" s="4">
         <v>999</v>
@@ -22823,10 +23053,10 @@
         </is>
       </c>
       <c r="G28" s="6">
+        <v>7</v>
+      </c>
+      <c r="H28" s="6">
         <v>14</v>
-      </c>
-      <c r="H28" s="6">
-        <v>7</v>
       </c>
       <c r="I28" s="4">
         <v>999</v>
@@ -22865,10 +23095,10 @@
         </is>
       </c>
       <c r="G29" s="6">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6">
         <v>10</v>
-      </c>
-      <c r="H29" s="6">
-        <v>0</v>
       </c>
       <c r="I29" s="4">
         <v>999</v>
@@ -22907,10 +23137,10 @@
         </is>
       </c>
       <c r="G30" s="6">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6">
         <v>10</v>
-      </c>
-      <c r="H30" s="6">
-        <v>0</v>
       </c>
       <c r="I30" s="4">
         <v>999</v>
@@ -22949,10 +23179,10 @@
         </is>
       </c>
       <c r="G31" s="6">
+        <v>2</v>
+      </c>
+      <c r="H31" s="6">
         <v>8</v>
-      </c>
-      <c r="H31" s="6">
-        <v>2</v>
       </c>
       <c r="I31" s="4">
         <v>877.1</v>
@@ -22991,10 +23221,10 @@
         </is>
       </c>
       <c r="G32" s="6">
+        <v>1</v>
+      </c>
+      <c r="H32" s="6">
         <v>6</v>
-      </c>
-      <c r="H32" s="6">
-        <v>1</v>
       </c>
       <c r="I32" s="4">
         <v>999</v>
@@ -23033,10 +23263,10 @@
         </is>
       </c>
       <c r="G33" s="6">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6">
         <v>8</v>
-      </c>
-      <c r="H33" s="6">
-        <v>0</v>
       </c>
       <c r="I33" s="4">
         <v>999</v>
@@ -23075,10 +23305,10 @@
         </is>
       </c>
       <c r="G34" s="6">
+        <v>1</v>
+      </c>
+      <c r="H34" s="6">
         <v>23</v>
-      </c>
-      <c r="H34" s="6">
-        <v>1</v>
       </c>
       <c r="I34" s="4">
         <v>999</v>
@@ -23117,10 +23347,10 @@
         </is>
       </c>
       <c r="G35" s="6">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6">
         <v>10</v>
-      </c>
-      <c r="H35" s="6">
-        <v>0</v>
       </c>
       <c r="I35" s="4">
         <v>999</v>
@@ -23159,10 +23389,10 @@
         </is>
       </c>
       <c r="G36" s="6">
+        <v>2</v>
+      </c>
+      <c r="H36" s="6">
         <v>4</v>
-      </c>
-      <c r="H36" s="6">
-        <v>2</v>
       </c>
       <c r="I36" s="4">
         <v>941.2</v>
@@ -23201,10 +23431,10 @@
         </is>
       </c>
       <c r="G37" s="6">
+        <v>6</v>
+      </c>
+      <c r="H37" s="6">
         <v>20</v>
-      </c>
-      <c r="H37" s="6">
-        <v>6</v>
       </c>
       <c r="I37" s="4">
         <v>999</v>
@@ -23243,10 +23473,10 @@
         </is>
       </c>
       <c r="G38" s="6">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6">
         <v>4</v>
-      </c>
-      <c r="H38" s="6">
-        <v>0</v>
       </c>
       <c r="I38" s="4">
         <v>999</v>
@@ -23285,10 +23515,10 @@
         </is>
       </c>
       <c r="G39" s="6">
+        <v>0</v>
+      </c>
+      <c r="H39" s="6">
         <v>9</v>
-      </c>
-      <c r="H39" s="6">
-        <v>0</v>
       </c>
       <c r="I39" s="4">
         <v>999</v>
@@ -23327,10 +23557,10 @@
         </is>
       </c>
       <c r="G40" s="6">
+        <v>7</v>
+      </c>
+      <c r="H40" s="6">
         <v>9</v>
-      </c>
-      <c r="H40" s="6">
-        <v>7</v>
       </c>
       <c r="I40" s="4">
         <v>999</v>
@@ -23369,10 +23599,10 @@
         </is>
       </c>
       <c r="G41" s="6">
+        <v>0</v>
+      </c>
+      <c r="H41" s="6">
         <v>8</v>
-      </c>
-      <c r="H41" s="6">
-        <v>0</v>
       </c>
       <c r="I41" s="4">
         <v>626.6</v>
@@ -23411,10 +23641,10 @@
         </is>
       </c>
       <c r="G42" s="6">
+        <v>1</v>
+      </c>
+      <c r="H42" s="6">
         <v>9</v>
-      </c>
-      <c r="H42" s="6">
-        <v>1</v>
       </c>
       <c r="I42" s="4">
         <v>999</v>
@@ -23453,10 +23683,10 @@
         </is>
       </c>
       <c r="G43" s="6">
+        <v>2</v>
+      </c>
+      <c r="H43" s="6">
         <v>18</v>
-      </c>
-      <c r="H43" s="6">
-        <v>2</v>
       </c>
       <c r="I43" s="4">
         <v>999</v>
@@ -23495,10 +23725,10 @@
         </is>
       </c>
       <c r="G44" s="6">
+        <v>0</v>
+      </c>
+      <c r="H44" s="6">
         <v>6</v>
-      </c>
-      <c r="H44" s="6">
-        <v>0</v>
       </c>
       <c r="I44" s="4">
         <v>999</v>
@@ -23537,10 +23767,10 @@
         </is>
       </c>
       <c r="G45" s="6">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6">
         <v>7</v>
-      </c>
-      <c r="H45" s="6">
-        <v>0</v>
       </c>
       <c r="I45" s="4">
         <v>999</v>
@@ -23579,10 +23809,10 @@
         </is>
       </c>
       <c r="G46" s="6">
+        <v>31</v>
+      </c>
+      <c r="H46" s="6">
         <v>51</v>
-      </c>
-      <c r="H46" s="6">
-        <v>31</v>
       </c>
       <c r="I46" s="4">
         <v>939.2</v>
@@ -23621,10 +23851,10 @@
         </is>
       </c>
       <c r="G47" s="6">
+        <v>2</v>
+      </c>
+      <c r="H47" s="6">
         <v>14</v>
-      </c>
-      <c r="H47" s="6">
-        <v>2</v>
       </c>
       <c r="I47" s="4">
         <v>966.8</v>
@@ -23663,10 +23893,10 @@
         </is>
       </c>
       <c r="G48" s="6">
+        <v>11</v>
+      </c>
+      <c r="H48" s="6">
         <v>19</v>
-      </c>
-      <c r="H48" s="6">
-        <v>11</v>
       </c>
       <c r="I48" s="4">
         <v>504.7</v>
@@ -23705,10 +23935,10 @@
         </is>
       </c>
       <c r="G49" s="6">
+        <v>29</v>
+      </c>
+      <c r="H49" s="6">
         <v>34</v>
-      </c>
-      <c r="H49" s="6">
-        <v>29</v>
       </c>
       <c r="I49" s="4">
         <v>999</v>
@@ -23747,10 +23977,10 @@
         </is>
       </c>
       <c r="G50" s="6">
+        <v>0</v>
+      </c>
+      <c r="H50" s="6">
         <v>4</v>
-      </c>
-      <c r="H50" s="6">
-        <v>0</v>
       </c>
       <c r="I50" s="4">
         <v>999</v>
@@ -23789,10 +24019,10 @@
         </is>
       </c>
       <c r="G51" s="6">
+        <v>0</v>
+      </c>
+      <c r="H51" s="6">
         <v>4</v>
-      </c>
-      <c r="H51" s="6">
-        <v>0</v>
       </c>
       <c r="I51" s="4">
         <v>999</v>
@@ -23831,10 +24061,10 @@
         </is>
       </c>
       <c r="G52" s="6">
+        <v>0</v>
+      </c>
+      <c r="H52" s="6">
         <v>21</v>
-      </c>
-      <c r="H52" s="6">
-        <v>0</v>
       </c>
       <c r="I52" s="4">
         <v>999</v>
@@ -23873,10 +24103,10 @@
         </is>
       </c>
       <c r="G53" s="6">
+        <v>0</v>
+      </c>
+      <c r="H53" s="6">
         <v>12</v>
-      </c>
-      <c r="H53" s="6">
-        <v>0</v>
       </c>
       <c r="I53" s="4">
         <v>670.5</v>
@@ -23915,10 +24145,10 @@
         </is>
       </c>
       <c r="G54" s="6">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6">
         <v>20</v>
-      </c>
-      <c r="H54" s="6">
-        <v>0</v>
       </c>
       <c r="I54" s="4">
         <v>999</v>
@@ -23957,10 +24187,10 @@
         </is>
       </c>
       <c r="G55" s="6">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6">
         <v>4</v>
-      </c>
-      <c r="H55" s="6">
-        <v>0</v>
       </c>
       <c r="I55" s="4">
         <v>999</v>
@@ -23999,10 +24229,10 @@
         </is>
       </c>
       <c r="G56" s="6">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6">
         <v>5</v>
-      </c>
-      <c r="H56" s="6">
-        <v>0</v>
       </c>
       <c r="I56" s="4">
         <v>999</v>
@@ -24041,10 +24271,10 @@
         </is>
       </c>
       <c r="G57" s="6">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6">
         <v>12</v>
-      </c>
-      <c r="H57" s="6">
-        <v>0</v>
       </c>
       <c r="I57" s="4">
         <v>753.1</v>
@@ -24083,10 +24313,10 @@
         </is>
       </c>
       <c r="G58" s="6">
+        <v>1</v>
+      </c>
+      <c r="H58" s="6">
         <v>19</v>
-      </c>
-      <c r="H58" s="6">
-        <v>1</v>
       </c>
       <c r="I58" s="4">
         <v>999</v>
@@ -24125,10 +24355,10 @@
         </is>
       </c>
       <c r="G59" s="6">
+        <v>6</v>
+      </c>
+      <c r="H59" s="6">
         <v>16</v>
-      </c>
-      <c r="H59" s="6">
-        <v>6</v>
       </c>
       <c r="I59" s="4">
         <v>999</v>
@@ -24167,10 +24397,10 @@
         </is>
       </c>
       <c r="G60" s="6">
+        <v>8</v>
+      </c>
+      <c r="H60" s="6">
         <v>33</v>
-      </c>
-      <c r="H60" s="6">
-        <v>8</v>
       </c>
       <c r="I60" s="4">
         <v>999</v>
@@ -24209,10 +24439,10 @@
         </is>
       </c>
       <c r="G61" s="6">
+        <v>0</v>
+      </c>
+      <c r="H61" s="6">
         <v>10</v>
-      </c>
-      <c r="H61" s="6">
-        <v>0</v>
       </c>
       <c r="I61" s="4">
         <v>999</v>
@@ -24251,10 +24481,10 @@
         </is>
       </c>
       <c r="G62" s="6">
+        <v>3</v>
+      </c>
+      <c r="H62" s="6">
         <v>9</v>
-      </c>
-      <c r="H62" s="6">
-        <v>3</v>
       </c>
       <c r="I62" s="4">
         <v>999</v>
@@ -24293,10 +24523,10 @@
         </is>
       </c>
       <c r="G63" s="6">
+        <v>3</v>
+      </c>
+      <c r="H63" s="6">
         <v>15</v>
-      </c>
-      <c r="H63" s="6">
-        <v>3</v>
       </c>
       <c r="I63" s="4">
         <v>999</v>
@@ -24335,10 +24565,10 @@
         </is>
       </c>
       <c r="G64" s="6">
+        <v>4</v>
+      </c>
+      <c r="H64" s="6">
         <v>16</v>
-      </c>
-      <c r="H64" s="6">
-        <v>4</v>
       </c>
       <c r="I64" s="4">
         <v>999</v>
@@ -24377,10 +24607,10 @@
         </is>
       </c>
       <c r="G65" s="6">
+        <v>8</v>
+      </c>
+      <c r="H65" s="6">
         <v>12</v>
-      </c>
-      <c r="H65" s="6">
-        <v>8</v>
       </c>
       <c r="I65" s="4">
         <v>714.7</v>
@@ -24419,10 +24649,10 @@
         </is>
       </c>
       <c r="G66" s="6">
+        <v>7</v>
+      </c>
+      <c r="H66" s="6">
         <v>21</v>
-      </c>
-      <c r="H66" s="6">
-        <v>7</v>
       </c>
       <c r="I66" s="4">
         <v>999</v>
@@ -24461,10 +24691,10 @@
         </is>
       </c>
       <c r="G67" s="6">
+        <v>2</v>
+      </c>
+      <c r="H67" s="6">
         <v>20</v>
-      </c>
-      <c r="H67" s="6">
-        <v>2</v>
       </c>
       <c r="I67" s="4">
         <v>999</v>
@@ -24503,10 +24733,10 @@
         </is>
       </c>
       <c r="G68" s="6">
+        <v>0</v>
+      </c>
+      <c r="H68" s="6">
         <v>10</v>
-      </c>
-      <c r="H68" s="6">
-        <v>0</v>
       </c>
       <c r="I68" s="4">
         <v>999</v>
@@ -24545,10 +24775,10 @@
         </is>
       </c>
       <c r="G69" s="6">
+        <v>0</v>
+      </c>
+      <c r="H69" s="6">
         <v>5</v>
-      </c>
-      <c r="H69" s="6">
-        <v>0</v>
       </c>
       <c r="I69" s="4">
         <v>999</v>
@@ -24587,10 +24817,10 @@
         </is>
       </c>
       <c r="G70" s="6">
+        <v>1</v>
+      </c>
+      <c r="H70" s="6">
         <v>4</v>
-      </c>
-      <c r="H70" s="6">
-        <v>1</v>
       </c>
       <c r="I70" s="4">
         <v>999</v>
@@ -24629,10 +24859,10 @@
         </is>
       </c>
       <c r="G71" s="6">
+        <v>0</v>
+      </c>
+      <c r="H71" s="6">
         <v>10</v>
-      </c>
-      <c r="H71" s="6">
-        <v>0</v>
       </c>
       <c r="I71" s="4">
         <v>999</v>
@@ -24671,10 +24901,10 @@
         </is>
       </c>
       <c r="G72" s="6">
+        <v>0</v>
+      </c>
+      <c r="H72" s="6">
         <v>20</v>
-      </c>
-      <c r="H72" s="6">
-        <v>0</v>
       </c>
       <c r="I72" s="4">
         <v>999</v>
@@ -24713,10 +24943,10 @@
         </is>
       </c>
       <c r="G73" s="6">
+        <v>2</v>
+      </c>
+      <c r="H73" s="6">
         <v>7</v>
-      </c>
-      <c r="H73" s="6">
-        <v>2</v>
       </c>
       <c r="I73" s="4">
         <v>999</v>
@@ -24755,10 +24985,10 @@
         </is>
       </c>
       <c r="G74" s="6">
+        <v>0</v>
+      </c>
+      <c r="H74" s="6">
         <v>5</v>
-      </c>
-      <c r="H74" s="6">
-        <v>0</v>
       </c>
       <c r="I74" s="4">
         <v>999</v>
@@ -24797,10 +25027,10 @@
         </is>
       </c>
       <c r="G75" s="6">
+        <v>0</v>
+      </c>
+      <c r="H75" s="6">
         <v>5</v>
-      </c>
-      <c r="H75" s="6">
-        <v>0</v>
       </c>
       <c r="I75" s="4">
         <v>999</v>
@@ -24839,10 +25069,10 @@
         </is>
       </c>
       <c r="G76" s="6">
+        <v>4</v>
+      </c>
+      <c r="H76" s="6">
         <v>6</v>
-      </c>
-      <c r="H76" s="6">
-        <v>4</v>
       </c>
       <c r="I76" s="4">
         <v>421.1</v>
@@ -24881,10 +25111,10 @@
         </is>
       </c>
       <c r="G77" s="6">
+        <v>0</v>
+      </c>
+      <c r="H77" s="6">
         <v>5</v>
-      </c>
-      <c r="H77" s="6">
-        <v>0</v>
       </c>
       <c r="I77" s="4">
         <v>999</v>
@@ -24923,10 +25153,10 @@
         </is>
       </c>
       <c r="G78" s="6">
+        <v>0</v>
+      </c>
+      <c r="H78" s="6">
         <v>6</v>
-      </c>
-      <c r="H78" s="6">
-        <v>0</v>
       </c>
       <c r="I78" s="4">
         <v>999</v>
@@ -24965,10 +25195,10 @@
         </is>
       </c>
       <c r="G79" s="6">
+        <v>0</v>
+      </c>
+      <c r="H79" s="6">
         <v>9</v>
-      </c>
-      <c r="H79" s="6">
-        <v>0</v>
       </c>
       <c r="I79" s="4">
         <v>999</v>
@@ -25007,10 +25237,10 @@
         </is>
       </c>
       <c r="G80" s="6">
+        <v>0</v>
+      </c>
+      <c r="H80" s="6">
         <v>10</v>
-      </c>
-      <c r="H80" s="6">
-        <v>0</v>
       </c>
       <c r="I80" s="4">
         <v>999</v>
@@ -25049,10 +25279,10 @@
         </is>
       </c>
       <c r="G81" s="6">
+        <v>30</v>
+      </c>
+      <c r="H81" s="6">
         <v>50</v>
-      </c>
-      <c r="H81" s="6">
-        <v>30</v>
       </c>
       <c r="I81" s="4">
         <v>999</v>
@@ -25091,10 +25321,10 @@
         </is>
       </c>
       <c r="G82" s="6">
+        <v>0</v>
+      </c>
+      <c r="H82" s="6">
         <v>5</v>
-      </c>
-      <c r="H82" s="6">
-        <v>0</v>
       </c>
       <c r="I82" s="4">
         <v>999</v>
@@ -25133,10 +25363,10 @@
         </is>
       </c>
       <c r="G83" s="6">
+        <v>1</v>
+      </c>
+      <c r="H83" s="6">
         <v>5</v>
-      </c>
-      <c r="H83" s="6">
-        <v>1</v>
       </c>
       <c r="I83" s="4">
         <v>546.8</v>
@@ -25175,10 +25405,10 @@
         </is>
       </c>
       <c r="G84" s="6">
+        <v>0</v>
+      </c>
+      <c r="H84" s="6">
         <v>4</v>
-      </c>
-      <c r="H84" s="6">
-        <v>0</v>
       </c>
       <c r="I84" s="4">
         <v>999</v>
@@ -25217,10 +25447,10 @@
         </is>
       </c>
       <c r="G85" s="6">
+        <v>0</v>
+      </c>
+      <c r="H85" s="6">
         <v>4</v>
-      </c>
-      <c r="H85" s="6">
-        <v>0</v>
       </c>
       <c r="I85" s="4">
         <v>999</v>
@@ -25259,10 +25489,10 @@
         </is>
       </c>
       <c r="G86" s="6">
+        <v>14</v>
+      </c>
+      <c r="H86" s="6">
         <v>314</v>
-      </c>
-      <c r="H86" s="6">
-        <v>14</v>
       </c>
       <c r="I86" s="4">
         <v>999</v>

--- a/Заявки поставщикам (авторасчёт).xlsx
+++ b/Заявки поставщикам (авторасчёт).xlsx
@@ -193,7 +193,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сегмент продаж</t>
+          <t xml:space="preserve">Рейтинг</t>
         </is>
       </c>
       <c r="M3" s="1" t="inlineStr">
@@ -233,7 +233,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H4" s="6">
@@ -290,7 +290,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H5" s="6">
@@ -347,7 +347,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H6" s="6">
@@ -404,7 +404,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H7" s="6">
@@ -461,7 +461,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H8" s="6">
@@ -518,7 +518,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H9" s="6">
@@ -575,7 +575,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H10" s="6">
@@ -632,7 +632,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H11" s="6">
@@ -689,7 +689,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H12" s="6">
@@ -746,7 +746,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H13" s="6">
@@ -803,7 +803,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H14" s="6">
@@ -860,7 +860,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H15" s="6">
@@ -917,7 +917,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H16" s="6">
@@ -974,7 +974,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H17" s="6">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H18" s="6">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H19" s="6">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H20" s="6">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H21" s="6">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H22" s="6">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H23" s="6">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H24" s="6">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H25" s="6">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H26" s="6">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H27" s="6">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H28" s="6">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H29" s="6">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H30" s="6">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H31" s="6">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H32" s="6">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H33" s="6">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H34" s="6">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H35" s="6">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H36" s="6">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H37" s="6">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H38" s="6">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H39" s="6">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H40" s="6">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H41" s="6">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H42" s="6">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H43" s="6">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H44" s="6">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H45" s="6">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H46" s="6">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H47" s="6">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H48" s="6">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H49" s="6">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H50" s="6">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H51" s="6">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H52" s="6">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H53" s="6">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ведро</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H54" s="6">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H55" s="6">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H56" s="6">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H57" s="6">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H58" s="6">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H59" s="6">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H60" s="6">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H61" s="6">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H62" s="6">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H63" s="6">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H64" s="6">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H65" s="6">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H66" s="6">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H67" s="6">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H68" s="6">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H69" s="6">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ведро</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H70" s="6">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H71" s="6">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H72" s="6">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H73" s="6">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ведро</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H74" s="6">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H75" s="6">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H76" s="6">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ведро</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H77" s="6">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ведро</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H78" s="6">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ведро</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H79" s="6">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ведро</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H80" s="6">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ведро</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H81" s="6">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H82" s="6">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H83" s="6">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H84" s="6">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H85" s="6">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H86" s="6">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H87" s="6">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H88" s="6">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H89" s="6">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H90" s="6">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H91" s="6">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H92" s="6">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H93" s="6">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бут</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H94" s="6">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H95" s="6">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H96" s="6">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H97" s="6">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H98" s="6">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H99" s="6">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H100" s="6">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H101" s="6">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H102" s="6">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H103" s="6">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H104" s="6">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H105" s="6">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H106" s="6">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H107" s="6">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H108" s="6">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H109" s="6">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H110" s="6">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бут</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H111" s="6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бут</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H112" s="6">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бут</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H113" s="6">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H114" s="6">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H115" s="6">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H116" s="6">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H117" s="6">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H118" s="6">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H119" s="6">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H120" s="6">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H121" s="6">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H122" s="6">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H123" s="6">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H124" s="6">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H125" s="6">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H126" s="6">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H127" s="6">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H128" s="6">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H129" s="6">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H130" s="6">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H131" s="6">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H132" s="6">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H133" s="6">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H134" s="6">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H135" s="6">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H136" s="6">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H137" s="6">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H138" s="6">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H139" s="6">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H140" s="6">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H141" s="6">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H142" s="6">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H143" s="6">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H144" s="6">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H145" s="6">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H146" s="6">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H147" s="6">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H148" s="6">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H149" s="6">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H150" s="6">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H151" s="6">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H152" s="6">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H153" s="6">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H154" s="6">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H155" s="6">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H156" s="6">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H157" s="6">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H158" s="6">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H159" s="6">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H160" s="6">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H161" s="6">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H162" s="6">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H163" s="6">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H164" s="6">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H165" s="6">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H166" s="6">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H167" s="6">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">банка</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H168" s="6">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H169" s="6">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H170" s="6">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H171" s="6">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H172" s="6">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H173" s="6">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H174" s="6">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H175" s="6">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H176" s="6">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H177" s="6">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H178" s="6">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H179" s="6">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H180" s="6">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H181" s="6">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H182" s="6">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H183" s="6">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H184" s="6">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H185" s="6">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H186" s="6">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H187" s="6">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H188" s="6">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H189" s="6">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H190" s="6">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H191" s="6">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H192" s="6">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H193" s="6">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H194" s="6">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H195" s="6">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H196" s="6">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H197" s="6">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H198" s="6">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H199" s="6">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H200" s="6">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H201" s="6">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H202" s="6">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H203" s="6">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H204" s="6">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H205" s="6">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H206" s="6">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H207" s="6">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H208" s="6">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H209" s="6">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H210" s="6">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H211" s="6">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H212" s="6">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H213" s="6">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H214" s="6">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H215" s="6">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H216" s="6">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H217" s="6">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H218" s="6">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H219" s="6">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H220" s="6">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H221" s="6">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H222" s="6">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H223" s="6">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H224" s="6">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H225" s="6">
@@ -12887,7 +12887,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H226" s="6">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H227" s="6">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H228" s="6">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H229" s="6">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H230" s="6">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H231" s="6">
@@ -13229,7 +13229,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H232" s="6">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H233" s="6">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H234" s="6">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H235" s="6">
@@ -13457,7 +13457,7 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H236" s="6">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H237" s="6">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H238" s="6">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H239" s="6">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H240" s="6">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H241" s="6">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H242" s="6">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H243" s="6">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H244" s="6">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H245" s="6">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H246" s="6">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H247" s="6">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H248" s="6">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H249" s="6">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H250" s="6">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H251" s="6">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H252" s="6">
@@ -14426,7 +14426,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H253" s="6">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H254" s="6">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H255" s="6">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H256" s="6">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H257" s="6">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H258" s="6">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H259" s="6">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H260" s="6">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H261" s="6">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H262" s="6">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H263" s="6">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H264" s="6">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H265" s="6">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H266" s="6">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H267" s="6">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H268" s="6">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H269" s="6">
@@ -15395,7 +15395,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H270" s="6">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H271" s="6">
@@ -15509,7 +15509,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H272" s="6">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H273" s="6">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H274" s="6">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H275" s="6">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H276" s="6">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H277" s="6">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H278" s="6">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H279" s="6">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H280" s="6">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H281" s="6">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H282" s="6">
@@ -16136,7 +16136,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H283" s="6">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H284" s="6">
@@ -16250,7 +16250,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H285" s="6">
@@ -16307,7 +16307,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H286" s="6">
@@ -16364,7 +16364,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H287" s="6">
@@ -16421,7 +16421,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H288" s="6">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H289" s="6">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H290" s="6">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H291" s="6">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H292" s="6">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H293" s="6">
@@ -16763,7 +16763,7 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H294" s="6">
@@ -16820,7 +16820,7 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H295" s="6">
@@ -16877,7 +16877,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H296" s="6">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H297" s="6">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H298" s="6">
@@ -17048,7 +17048,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H299" s="6">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H300" s="6">
@@ -17162,7 +17162,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H301" s="6">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H302" s="6">
@@ -17276,7 +17276,7 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H303" s="6">
@@ -17333,7 +17333,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H304" s="6">
@@ -17390,7 +17390,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H305" s="6">
@@ -17447,7 +17447,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H306" s="6">
@@ -17504,7 +17504,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H307" s="6">
@@ -17561,7 +17561,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H308" s="6">
@@ -17618,7 +17618,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H309" s="6">
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H310" s="6">
@@ -17732,7 +17732,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H311" s="6">
@@ -17789,7 +17789,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H312" s="6">
@@ -17846,7 +17846,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H313" s="6">
@@ -17903,7 +17903,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H314" s="6">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H315" s="6">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H316" s="6">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H317" s="6">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H318" s="6">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H319" s="6">
@@ -18245,7 +18245,7 @@
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H320" s="6">
@@ -18302,7 +18302,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H321" s="6">
@@ -18359,7 +18359,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H322" s="6">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H323" s="6">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H324" s="6">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H325" s="6">
@@ -18587,7 +18587,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H326" s="6">
@@ -18644,7 +18644,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H327" s="6">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H328" s="6">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H329" s="6">
@@ -18815,7 +18815,7 @@
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H330" s="6">
@@ -18872,7 +18872,7 @@
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H331" s="6">
@@ -18929,7 +18929,7 @@
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H332" s="6">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H333" s="6">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H334" s="6">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H335" s="6">
@@ -19157,7 +19157,7 @@
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H336" s="6">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H337" s="6">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H338" s="6">
@@ -19328,7 +19328,7 @@
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H339" s="6">
@@ -19385,7 +19385,7 @@
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H340" s="6">
@@ -19442,7 +19442,7 @@
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H341" s="6">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H342" s="6">
@@ -19556,7 +19556,7 @@
       </c>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H343" s="6">
@@ -19613,7 +19613,7 @@
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H344" s="6">
@@ -19670,7 +19670,7 @@
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H345" s="6">
@@ -19727,7 +19727,7 @@
       </c>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H346" s="6">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H347" s="6">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H348" s="6">
@@ -19898,7 +19898,7 @@
       </c>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H349" s="6">
@@ -19955,7 +19955,7 @@
       </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H350" s="6">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H351" s="6">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H352" s="6">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H353" s="6">
@@ -20183,7 +20183,7 @@
       </c>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H354" s="6">
@@ -20240,7 +20240,7 @@
       </c>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H355" s="6">
@@ -20297,7 +20297,7 @@
       </c>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H356" s="6">
@@ -20354,7 +20354,7 @@
       </c>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H357" s="6">
@@ -20411,7 +20411,7 @@
       </c>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H358" s="6">
@@ -20468,7 +20468,7 @@
       </c>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H359" s="6">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H360" s="6">
@@ -20582,7 +20582,7 @@
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H361" s="6">
@@ -20639,7 +20639,7 @@
       </c>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">шт</t>
+          <t xml:space="preserve">шт.</t>
         </is>
       </c>
       <c r="H362" s="6">
